--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128261987</v>
+        <v>136844352</v>
       </c>
       <c r="B2" t="n">
-        <v>92869</v>
+        <v>96565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>671861</v>
+        <v>672085</v>
       </c>
       <c r="R2" t="n">
-        <v>6648177</v>
+        <v>6648168</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261987</t>
+          <t>https://artportalen.se/Sighting/136844352</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128261988</v>
+        <v>136844358</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>96565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671922</v>
+        <v>672071</v>
       </c>
       <c r="R3" t="n">
-        <v>6648158</v>
+        <v>6648085</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +887,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261988</t>
+          <t>https://artportalen.se/Sighting/136844358</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128262008</v>
+        <v>136844364</v>
       </c>
       <c r="B4" t="n">
-        <v>91443</v>
+        <v>96565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5754</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671851</v>
+        <v>671939</v>
       </c>
       <c r="R4" t="n">
-        <v>6648067</v>
+        <v>6648121</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,18 +999,1374 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136844364</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128261987</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>671861</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6648177</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128261987</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128261988</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>671922</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6648158</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128261988</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128262008</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91443</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>671851</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6648067</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/128262008</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136844361</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>671949</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6648020</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844361</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136844366</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>671939</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6648124</v>
+      </c>
+      <c r="S9" t="n">
+        <v>69</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844366</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136844369</v>
+      </c>
+      <c r="B10" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>671875</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6648159</v>
+      </c>
+      <c r="S10" t="n">
+        <v>9</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ej stora träd</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844369</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136844370</v>
+      </c>
+      <c r="B11" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>671879</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6648093</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844370</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136844371</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>671904</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6648132</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Litet träd</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844371</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136844368</v>
+      </c>
+      <c r="B13" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>671875</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6648159</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844368</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136844348</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>671809</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6648285</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844348</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136844359</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>672071</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6648085</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844359</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136844365</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>671944</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6648126</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844365</t>
         </is>
       </c>
     </row>
@@ -989,6 +2375,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,32 +1016,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128261987</v>
+        <v>136975427</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>87425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671861</v>
+        <v>671934</v>
       </c>
       <c r="R5" t="n">
-        <v>6648177</v>
+        <v>6648022</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,38 +1122,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261987</t>
+          <t>https://artportalen.se/Sighting/136975427</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128261988</v>
+        <v>136975433</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>87425</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>671922</v>
+        <v>672028</v>
       </c>
       <c r="R6" t="n">
-        <v>6648158</v>
+        <v>6648071</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,12 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,16 +1234,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261988</t>
+          <t>https://artportalen.se/Sighting/136975433</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128262008</v>
+        <v>136975437</v>
       </c>
       <c r="B7" t="n">
-        <v>91443</v>
+        <v>87425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5754</v>
+        <v>3611</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>671851</v>
+        <v>672053</v>
       </c>
       <c r="R7" t="n">
-        <v>6648067</v>
+        <v>6648081</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,12 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,16 +1346,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128262008</t>
+          <t>https://artportalen.se/Sighting/136975437</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136844361</v>
+        <v>136975444</v>
       </c>
       <c r="B8" t="n">
-        <v>93447</v>
+        <v>87425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,46 +1363,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>3611</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>671949</v>
+        <v>672012</v>
       </c>
       <c r="R8" t="n">
-        <v>6648020</v>
+        <v>6648146</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1396,22 +1417,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,74 +1447,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844361</t>
+          <t>https://artportalen.se/Sighting/136975444</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136844366</v>
+        <v>136975446</v>
       </c>
       <c r="B9" t="n">
-        <v>107064</v>
+        <v>87425</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>3611</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>671939</v>
+        <v>671945</v>
       </c>
       <c r="R9" t="n">
-        <v>6648124</v>
+        <v>6648123</v>
       </c>
       <c r="S9" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1517,22 +1529,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,74 +1559,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844366</t>
+          <t>https://artportalen.se/Sighting/136975446</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136844369</v>
+        <v>136975440</v>
       </c>
       <c r="B10" t="n">
-        <v>107064</v>
+        <v>87324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>3762</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>671875</v>
+        <v>672040</v>
       </c>
       <c r="R10" t="n">
-        <v>6648159</v>
+        <v>6648115</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,27 +1641,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ej stora träd</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1673,66 +1671,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844369</t>
+          <t>https://artportalen.se/Sighting/136975440</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136844370</v>
+        <v>136975447</v>
       </c>
       <c r="B11" t="n">
-        <v>107064</v>
+        <v>87324</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220785</v>
+        <v>3762</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671879</v>
+        <v>671890</v>
       </c>
       <c r="R11" t="n">
-        <v>6648093</v>
+        <v>6648080</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1759,22 +1753,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,56 +1777,55 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844370</t>
+          <t>https://artportalen.se/Sighting/136975447</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136844371</v>
+        <v>136975443</v>
       </c>
       <c r="B12" t="n">
-        <v>107064</v>
+        <v>93423</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1842,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671904</v>
+        <v>672026</v>
       </c>
       <c r="R12" t="n">
-        <v>6648132</v>
+        <v>6648149</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1872,27 +1865,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Litet träd</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,27 +1895,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844371</t>
+          <t>https://artportalen.se/Sighting/136975443</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136844368</v>
+        <v>128261987</v>
       </c>
       <c r="B13" t="n">
-        <v>104876</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1935,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1959,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671875</v>
+        <v>671861</v>
       </c>
       <c r="R13" t="n">
-        <v>6648159</v>
+        <v>6648177</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1989,22 +1977,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,27 +1997,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844368</t>
+          <t>https://artportalen.se/Sighting/128261987</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136844348</v>
+        <v>128261988</v>
       </c>
       <c r="B14" t="n">
-        <v>101563</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2047,21 +2025,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2071,13 +2049,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671809</v>
+        <v>671922</v>
       </c>
       <c r="R14" t="n">
-        <v>6648285</v>
+        <v>6648158</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2101,22 +2079,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:11</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,49 +2099,49 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844348</t>
+          <t>https://artportalen.se/Sighting/128261988</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136844359</v>
+        <v>128262008</v>
       </c>
       <c r="B15" t="n">
-        <v>101563</v>
+        <v>91443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>5754</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2183,13 +2151,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672071</v>
+        <v>671851</v>
       </c>
       <c r="R15" t="n">
-        <v>6648085</v>
+        <v>6648067</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2213,22 +2181,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,62 +2201,71 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844359</t>
+          <t>https://artportalen.se/Sighting/128262008</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136844365</v>
+        <v>136844361</v>
       </c>
       <c r="B16" t="n">
-        <v>101563</v>
+        <v>93447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>671944</v>
+        <v>671949</v>
       </c>
       <c r="R16" t="n">
-        <v>6648126</v>
+        <v>6648020</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2330,7 +2297,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2307,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2365,6 +2332,1607 @@
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844361</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136975430</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>671947</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6648018</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975430</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136975432</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>672011</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6648066</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975432</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136975436</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>672043</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6648077</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975436</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136975439</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>672064</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6648093</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975439</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136975452</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93447</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>671811</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6648068</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975452</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136844366</v>
+      </c>
+      <c r="B22" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>671939</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6648124</v>
+      </c>
+      <c r="S22" t="n">
+        <v>69</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844366</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136844369</v>
+      </c>
+      <c r="B23" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>671875</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6648159</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ej stora träd</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844369</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136844370</v>
+      </c>
+      <c r="B24" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>671879</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6648093</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844370</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136844371</v>
+      </c>
+      <c r="B25" t="n">
+        <v>107064</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>671904</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6648132</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Litet träd</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844371</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136844368</v>
+      </c>
+      <c r="B26" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>671875</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6648159</v>
+      </c>
+      <c r="S26" t="n">
+        <v>7</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844368</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136975429</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>671936</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6648021</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975429</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136844348</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>671809</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6648285</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844348</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136844359</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>672071</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6648085</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844359</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136844365</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>671944</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6648126</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136844365</t>
         </is>
@@ -2387,6 +3955,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136844352</v>
       </c>
       <c r="B2" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844358</v>
       </c>
       <c r="B3" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844364</v>
       </c>
       <c r="B4" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136975427</v>
       </c>
       <c r="B5" t="n">
-        <v>87425</v>
+        <v>87427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975433</v>
       </c>
       <c r="B6" t="n">
-        <v>87425</v>
+        <v>87427</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975437</v>
       </c>
       <c r="B7" t="n">
-        <v>87425</v>
+        <v>87427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975444</v>
       </c>
       <c r="B8" t="n">
-        <v>87425</v>
+        <v>87427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975446</v>
       </c>
       <c r="B9" t="n">
-        <v>87425</v>
+        <v>87427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975440</v>
       </c>
       <c r="B10" t="n">
-        <v>87324</v>
+        <v>87326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136975447</v>
       </c>
       <c r="B11" t="n">
-        <v>87324</v>
+        <v>87326</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136975443</v>
       </c>
       <c r="B12" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>136844361</v>
       </c>
       <c r="B16" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,7 +2342,7 @@
         <v>136975430</v>
       </c>
       <c r="B17" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         <v>136975432</v>
       </c>
       <c r="B18" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         <v>136975436</v>
       </c>
       <c r="B19" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         <v>136975439</v>
       </c>
       <c r="B20" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>136975452</v>
       </c>
       <c r="B21" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>136844366</v>
       </c>
       <c r="B22" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>136844369</v>
       </c>
       <c r="B23" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>136844370</v>
       </c>
       <c r="B24" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>136844371</v>
       </c>
       <c r="B25" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>136844368</v>
       </c>
       <c r="B26" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>136975429</v>
       </c>
       <c r="B27" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>136844348</v>
       </c>
       <c r="B28" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>136844359</v>
       </c>
       <c r="B29" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3831,7 +3831,7 @@
         <v>136844365</v>
       </c>
       <c r="B30" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136844352</v>
       </c>
       <c r="B2" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844358</v>
       </c>
       <c r="B3" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844364</v>
       </c>
       <c r="B4" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136975427</v>
       </c>
       <c r="B5" t="n">
-        <v>87427</v>
+        <v>87429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975433</v>
       </c>
       <c r="B6" t="n">
-        <v>87427</v>
+        <v>87429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975437</v>
       </c>
       <c r="B7" t="n">
-        <v>87427</v>
+        <v>87429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975444</v>
       </c>
       <c r="B8" t="n">
-        <v>87427</v>
+        <v>87429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975446</v>
       </c>
       <c r="B9" t="n">
-        <v>87427</v>
+        <v>87429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136975440</v>
+        <v>137064512</v>
       </c>
       <c r="B10" t="n">
-        <v>87326</v>
+        <v>87491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672040</v>
+        <v>671859</v>
       </c>
       <c r="R10" t="n">
-        <v>6648115</v>
+        <v>6648162</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1641,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1671,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975440</t>
+          <t>https://artportalen.se/Sighting/137064512</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136975447</v>
+        <v>136975440</v>
       </c>
       <c r="B11" t="n">
-        <v>87326</v>
+        <v>87328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671890</v>
+        <v>672040</v>
       </c>
       <c r="R11" t="n">
-        <v>6648080</v>
+        <v>6648115</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1794,38 +1794,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975447</t>
+          <t>https://artportalen.se/Sighting/136975440</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136975443</v>
+        <v>136975447</v>
       </c>
       <c r="B12" t="n">
-        <v>93425</v>
+        <v>87328</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>3762</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672026</v>
+        <v>671890</v>
       </c>
       <c r="R12" t="n">
-        <v>6648149</v>
+        <v>6648080</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,16 +1906,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975443</t>
+          <t>https://artportalen.se/Sighting/136975447</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128261987</v>
+        <v>137064514</v>
       </c>
       <c r="B13" t="n">
-        <v>92869</v>
+        <v>93411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>4363</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,13 +1947,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671861</v>
+        <v>671858</v>
       </c>
       <c r="R13" t="n">
-        <v>6648177</v>
+        <v>6648190</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,12 +1977,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,49 +2007,49 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261987</t>
+          <t>https://artportalen.se/Sighting/137064514</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128261988</v>
+        <v>136975443</v>
       </c>
       <c r="B14" t="n">
-        <v>92869</v>
+        <v>93427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2049,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671922</v>
+        <v>672026</v>
       </c>
       <c r="R14" t="n">
-        <v>6648158</v>
+        <v>6648149</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2079,12 +2089,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2110,38 +2130,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261988</t>
+          <t>https://artportalen.se/Sighting/136975443</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128262008</v>
+        <v>128261987</v>
       </c>
       <c r="B15" t="n">
-        <v>91443</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5754</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2151,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>671851</v>
+        <v>671861</v>
       </c>
       <c r="R15" t="n">
-        <v>6648067</v>
+        <v>6648177</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2212,63 +2232,54 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128262008</t>
+          <t>https://artportalen.se/Sighting/128261987</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136844361</v>
+        <v>128261988</v>
       </c>
       <c r="B16" t="n">
-        <v>93449</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>671949</v>
+        <v>671922</v>
       </c>
       <c r="R16" t="n">
-        <v>6648020</v>
+        <v>6648158</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2292,22 +2303,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2322,49 +2323,49 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844361</t>
+          <t>https://artportalen.se/Sighting/128261988</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136975430</v>
+        <v>137064508</v>
       </c>
       <c r="B17" t="n">
-        <v>93449</v>
+        <v>93087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2374,13 +2375,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>671947</v>
+        <v>672061</v>
       </c>
       <c r="R17" t="n">
-        <v>6648018</v>
+        <v>6648256</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2404,22 +2405,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2434,49 +2435,49 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975430</t>
+          <t>https://artportalen.se/Sighting/137064508</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136975432</v>
+        <v>137064519</v>
       </c>
       <c r="B18" t="n">
-        <v>93449</v>
+        <v>93087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2486,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672011</v>
+        <v>671801</v>
       </c>
       <c r="R18" t="n">
-        <v>6648066</v>
+        <v>6648156</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2516,22 +2517,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2546,49 +2547,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975432</t>
+          <t>https://artportalen.se/Sighting/137064519</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136975436</v>
+        <v>137064517</v>
       </c>
       <c r="B19" t="n">
-        <v>93449</v>
+        <v>91624</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2598,13 +2599,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672043</v>
+        <v>671764</v>
       </c>
       <c r="R19" t="n">
-        <v>6648077</v>
+        <v>6648252</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2628,22 +2629,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2658,27 +2659,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975436</t>
+          <t>https://artportalen.se/Sighting/137064517</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136975439</v>
+        <v>128262008</v>
       </c>
       <c r="B20" t="n">
-        <v>93449</v>
+        <v>91443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2686,21 +2687,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2710,13 +2711,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672064</v>
+        <v>671851</v>
       </c>
       <c r="R20" t="n">
-        <v>6648093</v>
+        <v>6648067</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2740,22 +2741,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:05</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,16 +2772,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975439</t>
+          <t>https://artportalen.se/Sighting/128262008</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136975452</v>
+        <v>136844361</v>
       </c>
       <c r="B21" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2815,17 +2806,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>671811</v>
+        <v>671949</v>
       </c>
       <c r="R21" t="n">
-        <v>6648068</v>
+        <v>6648020</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2852,22 +2852,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,74 +2882,65 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975452</t>
+          <t>https://artportalen.se/Sighting/136844361</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136844366</v>
+        <v>136975430</v>
       </c>
       <c r="B22" t="n">
-        <v>107070</v>
+        <v>93451</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>671939</v>
+        <v>671947</v>
       </c>
       <c r="R22" t="n">
-        <v>6648124</v>
+        <v>6648018</v>
       </c>
       <c r="S22" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2973,22 +2964,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3003,74 +2994,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844366</t>
+          <t>https://artportalen.se/Sighting/136975430</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136844369</v>
+        <v>136975432</v>
       </c>
       <c r="B23" t="n">
-        <v>107070</v>
+        <v>93451</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>671875</v>
+        <v>672011</v>
       </c>
       <c r="R23" t="n">
-        <v>6648159</v>
+        <v>6648066</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3094,27 +3076,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ej stora träd</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3129,66 +3106,62 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844369</t>
+          <t>https://artportalen.se/Sighting/136975432</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136844370</v>
+        <v>136975436</v>
       </c>
       <c r="B24" t="n">
-        <v>107070</v>
+        <v>93451</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>671879</v>
+        <v>672043</v>
       </c>
       <c r="R24" t="n">
-        <v>6648093</v>
+        <v>6648077</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3215,22 +3188,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3239,56 +3212,55 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844370</t>
+          <t>https://artportalen.se/Sighting/136975436</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136844371</v>
+        <v>136975439</v>
       </c>
       <c r="B25" t="n">
-        <v>107070</v>
+        <v>93451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3298,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>671904</v>
+        <v>672064</v>
       </c>
       <c r="R25" t="n">
-        <v>6648132</v>
+        <v>6648093</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3328,27 +3300,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Litet träd</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,49 +3330,49 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844371</t>
+          <t>https://artportalen.se/Sighting/136975439</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136844368</v>
+        <v>136975452</v>
       </c>
       <c r="B26" t="n">
-        <v>104882</v>
+        <v>93451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3415,13 +3382,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>671875</v>
+        <v>671811</v>
       </c>
       <c r="R26" t="n">
-        <v>6648159</v>
+        <v>6648068</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3445,22 +3412,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,49 +3442,49 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844368</t>
+          <t>https://artportalen.se/Sighting/136975452</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136975429</v>
+        <v>137064507</v>
       </c>
       <c r="B27" t="n">
-        <v>104882</v>
+        <v>93451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3527,13 +3494,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>671936</v>
+        <v>671946</v>
       </c>
       <c r="R27" t="n">
-        <v>6648021</v>
+        <v>6648016</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3557,22 +3524,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,49 +3554,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975429</t>
+          <t>https://artportalen.se/Sighting/137064507</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136844348</v>
+        <v>137064509</v>
       </c>
       <c r="B28" t="n">
-        <v>101569</v>
+        <v>93451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3639,13 +3606,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>671809</v>
+        <v>671985</v>
       </c>
       <c r="R28" t="n">
-        <v>6648285</v>
+        <v>6648131</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3669,22 +3636,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,49 +3666,49 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844348</t>
+          <t>https://artportalen.se/Sighting/137064509</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136844359</v>
+        <v>137064510</v>
       </c>
       <c r="B29" t="n">
-        <v>101569</v>
+        <v>93451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3751,13 +3718,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672071</v>
+        <v>672002</v>
       </c>
       <c r="R29" t="n">
-        <v>6648085</v>
+        <v>6648119</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,22 +3748,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,49 +3778,49 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844359</t>
+          <t>https://artportalen.se/Sighting/137064510</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136844365</v>
+        <v>137064511</v>
       </c>
       <c r="B30" t="n">
-        <v>101569</v>
+        <v>93451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3863,13 +3830,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>671944</v>
+        <v>672003</v>
       </c>
       <c r="R30" t="n">
-        <v>6648126</v>
+        <v>6648111</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3893,22 +3860,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3923,16 +3890,1505 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064511</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137064516</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>671772</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6648263</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064516</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137064518</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>671781</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6648217</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064518</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137064515</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99384</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>671859</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6648188</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064515</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136844366</v>
+      </c>
+      <c r="B34" t="n">
+        <v>107072</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>671939</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6648124</v>
+      </c>
+      <c r="S34" t="n">
+        <v>69</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844366</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136844369</v>
+      </c>
+      <c r="B35" t="n">
+        <v>107072</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>671875</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6648159</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ej stora träd</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844369</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136844370</v>
+      </c>
+      <c r="B36" t="n">
+        <v>107072</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>671879</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6648093</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844370</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136844371</v>
+      </c>
+      <c r="B37" t="n">
+        <v>107072</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>671904</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6648132</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Litet träd</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844371</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>136844368</v>
+      </c>
+      <c r="B38" t="n">
+        <v>104884</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>671875</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6648159</v>
+      </c>
+      <c r="S38" t="n">
+        <v>7</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844368</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>136975429</v>
+      </c>
+      <c r="B39" t="n">
+        <v>104884</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>671936</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6648021</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975429</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137064513</v>
+      </c>
+      <c r="B40" t="n">
+        <v>104884</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>671855</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6648166</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064513</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>136844348</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>671809</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6648285</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844348</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136844359</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>672071</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6648085</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844359</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136844365</v>
+      </c>
+      <c r="B43" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>671944</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6648126</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136844365</t>
         </is>
@@ -3969,6 +5425,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136844352</v>
+        <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>96573</v>
+        <v>87504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2812</v>
+        <v>1988</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672085</v>
+        <v>672005</v>
       </c>
       <c r="R2" t="n">
-        <v>6648168</v>
+        <v>6648054</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,24 +775,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844352</t>
+          <t>https://artportalen.se/Sighting/137074588</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136844358</v>
+        <v>136844352</v>
       </c>
       <c r="B3" t="n">
         <v>96573</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672071</v>
+        <v>672085</v>
       </c>
       <c r="R3" t="n">
-        <v>6648085</v>
+        <v>6648168</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,13 +898,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844358</t>
+          <t>https://artportalen.se/Sighting/136844352</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136844364</v>
+        <v>136844358</v>
       </c>
       <c r="B4" t="n">
         <v>96573</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671939</v>
+        <v>672071</v>
       </c>
       <c r="R4" t="n">
-        <v>6648121</v>
+        <v>6648085</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,38 +1010,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844364</t>
+          <t>https://artportalen.se/Sighting/136844358</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136975427</v>
+        <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>87429</v>
+        <v>96573</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3611</v>
+        <v>2812</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671934</v>
+        <v>671939</v>
       </c>
       <c r="R5" t="n">
-        <v>6648022</v>
+        <v>6648121</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,24 +1111,24 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975427</t>
+          <t>https://artportalen.se/Sighting/136844364</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136975433</v>
+        <v>136975427</v>
       </c>
       <c r="B6" t="n">
         <v>87429</v>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672028</v>
+        <v>671934</v>
       </c>
       <c r="R6" t="n">
-        <v>6648071</v>
+        <v>6648022</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,13 +1234,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975433</t>
+          <t>https://artportalen.se/Sighting/136975427</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136975437</v>
+        <v>136975433</v>
       </c>
       <c r="B7" t="n">
         <v>87429</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672053</v>
+        <v>672028</v>
       </c>
       <c r="R7" t="n">
-        <v>6648081</v>
+        <v>6648071</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,13 +1346,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975437</t>
+          <t>https://artportalen.se/Sighting/136975433</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136975444</v>
+        <v>136975437</v>
       </c>
       <c r="B8" t="n">
         <v>87429</v>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672012</v>
+        <v>672053</v>
       </c>
       <c r="R8" t="n">
-        <v>6648146</v>
+        <v>6648081</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,13 +1458,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975444</t>
+          <t>https://artportalen.se/Sighting/136975437</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136975446</v>
+        <v>136975444</v>
       </c>
       <c r="B9" t="n">
         <v>87429</v>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>671945</v>
+        <v>672012</v>
       </c>
       <c r="R9" t="n">
-        <v>6648123</v>
+        <v>6648146</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,38 +1570,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975446</t>
+          <t>https://artportalen.se/Sighting/136975444</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137064512</v>
+        <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87491</v>
+        <v>87429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3674</v>
+        <v>3611</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>671859</v>
+        <v>671945</v>
       </c>
       <c r="R10" t="n">
-        <v>6648162</v>
+        <v>6648123</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1641,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,65 +1671,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064512</t>
+          <t>https://artportalen.se/Sighting/136975446</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136975440</v>
+        <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87328</v>
+        <v>87429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3762</v>
+        <v>3611</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672040</v>
+        <v>672048</v>
       </c>
       <c r="R11" t="n">
-        <v>6648115</v>
+        <v>6648081</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,22 +1753,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,57 +1788,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975440</t>
+          <t>https://artportalen.se/Sighting/137074577</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136975447</v>
+        <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87328</v>
+        <v>87429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3762</v>
+        <v>3611</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671890</v>
+        <v>671941</v>
       </c>
       <c r="R12" t="n">
-        <v>6648080</v>
+        <v>6648132</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1865,22 +1865,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1900,60 +1900,60 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975447</t>
+          <t>https://artportalen.se/Sighting/137074598</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137064514</v>
+        <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>93411</v>
+        <v>87429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4363</v>
+        <v>3611</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>671858</v>
+        <v>671941</v>
       </c>
       <c r="R13" t="n">
-        <v>6648190</v>
+        <v>6648015</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,27 +2007,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064514</t>
+          <t>https://artportalen.se/Sighting/137074599</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136975443</v>
+        <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>93427</v>
+        <v>87429</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,34 +2035,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>3611</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672026</v>
+        <v>671934</v>
       </c>
       <c r="R14" t="n">
-        <v>6648149</v>
+        <v>6648133</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2089,22 +2089,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2124,60 +2124,60 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975443</t>
+          <t>https://artportalen.se/Sighting/137074600</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128261987</v>
+        <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>92869</v>
+        <v>87429</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>671861</v>
+        <v>671864</v>
       </c>
       <c r="R15" t="n">
-        <v>6648177</v>
+        <v>6648176</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2201,12 +2201,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2226,60 +2236,60 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261987</t>
+          <t>https://artportalen.se/Sighting/137074609</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128261988</v>
+        <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>92869</v>
+        <v>87429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>3611</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cortinarius elegantior</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>671922</v>
+        <v>671857</v>
       </c>
       <c r="R16" t="n">
-        <v>6648158</v>
+        <v>6648183</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2303,12 +2313,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2328,22 +2348,22 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261988</t>
+          <t>https://artportalen.se/Sighting/137074611</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137064508</v>
+        <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>93087</v>
+        <v>87594</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2351,37 +2371,33 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>3624</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672061</v>
+        <v>672057</v>
       </c>
       <c r="R17" t="n">
-        <v>6648256</v>
+        <v>6648177</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,7 +2426,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,7 +2436,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2435,27 +2451,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064508</t>
+          <t>https://artportalen.se/Sighting/137074573</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137064519</v>
+        <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>93087</v>
+        <v>87594</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,37 +2479,33 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>3624</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>671801</v>
+        <v>671847</v>
       </c>
       <c r="R18" t="n">
-        <v>6648156</v>
+        <v>6648222</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2534,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2544,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2547,49 +2559,49 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064519</t>
+          <t>https://artportalen.se/Sighting/137074619</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137064517</v>
+        <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>91624</v>
+        <v>87491</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5747</v>
+        <v>3674</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2599,13 +2611,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>671764</v>
+        <v>671859</v>
       </c>
       <c r="R19" t="n">
-        <v>6648252</v>
+        <v>6648162</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,7 +2646,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,7 +2656,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2670,54 +2682,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064517</t>
+          <t>https://artportalen.se/Sighting/137064512</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128262008</v>
+        <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>91443</v>
+        <v>87491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5754</v>
+        <v>3674</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>671851</v>
+        <v>671821</v>
       </c>
       <c r="R20" t="n">
-        <v>6648067</v>
+        <v>6648299</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,12 +2753,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2766,66 +2788,57 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128262008</t>
+          <t>https://artportalen.se/Sighting/137074621</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136844361</v>
+        <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>93451</v>
+        <v>87328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>671949</v>
+        <v>672040</v>
       </c>
       <c r="R21" t="n">
-        <v>6648020</v>
+        <v>6648115</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2852,22 +2865,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2882,49 +2895,49 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844361</t>
+          <t>https://artportalen.se/Sighting/136975440</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136975430</v>
+        <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>93451</v>
+        <v>87328</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2934,10 +2947,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>671947</v>
+        <v>671890</v>
       </c>
       <c r="R22" t="n">
-        <v>6648018</v>
+        <v>6648080</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2969,7 +2982,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2992,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3005,51 +3018,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975430</t>
+          <t>https://artportalen.se/Sighting/136975447</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136975432</v>
+        <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>93451</v>
+        <v>87328</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672011</v>
+        <v>671933</v>
       </c>
       <c r="R23" t="n">
-        <v>6648066</v>
+        <v>6648176</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3076,22 +3089,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3111,57 +3124,57 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975432</t>
+          <t>https://artportalen.se/Sighting/137074601</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136975436</v>
+        <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>93451</v>
+        <v>87328</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672043</v>
+        <v>671852</v>
       </c>
       <c r="R24" t="n">
-        <v>6648077</v>
+        <v>6648189</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3188,22 +3201,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3223,57 +3236,57 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975436</t>
+          <t>https://artportalen.se/Sighting/137074617</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136975439</v>
+        <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>93451</v>
+        <v>87328</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672064</v>
+        <v>671851</v>
       </c>
       <c r="R25" t="n">
-        <v>6648093</v>
+        <v>6648181</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3300,22 +3313,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,57 +3348,57 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975439</t>
+          <t>https://artportalen.se/Sighting/137074618</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136975452</v>
+        <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>93451</v>
+        <v>87328</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>671811</v>
+        <v>671821</v>
       </c>
       <c r="R26" t="n">
-        <v>6648068</v>
+        <v>6648299</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3412,22 +3425,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3447,60 +3460,60 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975452</t>
+          <t>https://artportalen.se/Sighting/137074622</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137064507</v>
+        <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>93451</v>
+        <v>87328</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5964</v>
+        <v>3762</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>671946</v>
+        <v>671815</v>
       </c>
       <c r="R27" t="n">
-        <v>6648016</v>
+        <v>6648070</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3529,7 +3542,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3539,7 +3552,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3554,49 +3567,49 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064507</t>
+          <t>https://artportalen.se/Sighting/137074628</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137064509</v>
+        <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93451</v>
+        <v>93411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3606,13 +3619,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>671985</v>
+        <v>671858</v>
       </c>
       <c r="R28" t="n">
-        <v>6648131</v>
+        <v>6648190</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3641,7 +3654,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3651,7 +3664,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3677,54 +3690,54 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064509</t>
+          <t>https://artportalen.se/Sighting/137064514</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137064510</v>
+        <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93451</v>
+        <v>93411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>4363</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672002</v>
+        <v>671856</v>
       </c>
       <c r="R29" t="n">
-        <v>6648119</v>
+        <v>6648181</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3753,7 +3766,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3763,7 +3776,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3778,27 +3791,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064510</t>
+          <t>https://artportalen.se/Sighting/137074612</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137064511</v>
+        <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93451</v>
+        <v>93427</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3806,21 +3819,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3830,13 +3843,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672003</v>
+        <v>672026</v>
       </c>
       <c r="R30" t="n">
-        <v>6648111</v>
+        <v>6648149</v>
       </c>
       <c r="S30" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3860,22 +3873,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3890,49 +3903,49 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064511</t>
+          <t>https://artportalen.se/Sighting/136975443</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137064516</v>
+        <v>128261987</v>
       </c>
       <c r="B31" t="n">
-        <v>93451</v>
+        <v>92869</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3942,10 +3955,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>671772</v>
+        <v>671861</v>
       </c>
       <c r="R31" t="n">
-        <v>6648263</v>
+        <v>6648177</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3972,22 +3985,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:27</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4002,27 +4005,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064516</t>
+          <t>https://artportalen.se/Sighting/128261987</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137064518</v>
+        <v>128261988</v>
       </c>
       <c r="B32" t="n">
-        <v>5182</v>
+        <v>92869</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4030,21 +4033,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>4769</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4054,13 +4057,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>671781</v>
+        <v>671922</v>
       </c>
       <c r="R32" t="n">
-        <v>6648217</v>
+        <v>6648158</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4084,22 +4087,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:42</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4114,27 +4107,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064518</t>
+          <t>https://artportalen.se/Sighting/128261988</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137064515</v>
+        <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>99384</v>
+        <v>93087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4142,21 +4135,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219862</v>
+        <v>4769</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4166,13 +4159,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>671859</v>
+        <v>672061</v>
       </c>
       <c r="R33" t="n">
-        <v>6648188</v>
+        <v>6648256</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4201,7 +4194,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4211,7 +4204,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4237,63 +4230,54 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064515</t>
+          <t>https://artportalen.se/Sighting/137064508</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136844366</v>
+        <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>107072</v>
+        <v>93087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220785</v>
+        <v>4769</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>671939</v>
+        <v>671801</v>
       </c>
       <c r="R34" t="n">
-        <v>6648124</v>
+        <v>6648156</v>
       </c>
       <c r="S34" t="n">
-        <v>69</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4317,22 +4301,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4347,74 +4331,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844366</t>
+          <t>https://artportalen.se/Sighting/137064519</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136844369</v>
+        <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>107072</v>
+        <v>93087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220785</v>
+        <v>4769</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>671875</v>
+        <v>672006</v>
       </c>
       <c r="R35" t="n">
-        <v>6648159</v>
+        <v>6648070</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4438,27 +4413,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ej stora träd</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4473,69 +4443,65 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844369</t>
+          <t>https://artportalen.se/Sighting/137074584</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136844370</v>
+        <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>107072</v>
+        <v>93087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220785</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>671879</v>
+        <v>671908</v>
       </c>
       <c r="R36" t="n">
-        <v>6648093</v>
+        <v>6647988</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4559,22 +4525,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4583,69 +4549,68 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844370</t>
+          <t>https://artportalen.se/Sighting/137074604</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136844371</v>
+        <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>107072</v>
+        <v>91598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220785</v>
+        <v>5741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>671904</v>
+        <v>671999</v>
       </c>
       <c r="R37" t="n">
-        <v>6648132</v>
+        <v>6648163</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4672,27 +4637,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Litet träd</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4707,49 +4667,49 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844371</t>
+          <t>https://artportalen.se/Sighting/137074592</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136844368</v>
+        <v>137064517</v>
       </c>
       <c r="B38" t="n">
-        <v>104884</v>
+        <v>91624</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4759,13 +4719,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>671875</v>
+        <v>671764</v>
       </c>
       <c r="R38" t="n">
-        <v>6648159</v>
+        <v>6648252</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4789,22 +4749,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4819,62 +4779,62 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844368</t>
+          <t>https://artportalen.se/Sighting/137064517</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136975429</v>
+        <v>137074636</v>
       </c>
       <c r="B39" t="n">
-        <v>104884</v>
+        <v>91624</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>671936</v>
+        <v>671767</v>
       </c>
       <c r="R39" t="n">
-        <v>6648021</v>
+        <v>6648247</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4901,22 +4861,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4936,44 +4896,44 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975429</t>
+          <t>https://artportalen.se/Sighting/137074636</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137064513</v>
+        <v>128262008</v>
       </c>
       <c r="B40" t="n">
-        <v>104884</v>
+        <v>91443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222412</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4983,13 +4943,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>671855</v>
+        <v>671851</v>
       </c>
       <c r="R40" t="n">
-        <v>6648166</v>
+        <v>6648067</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5013,22 +4973,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:19</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5043,62 +4993,71 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064513</t>
+          <t>https://artportalen.se/Sighting/128262008</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136844348</v>
+        <v>136844361</v>
       </c>
       <c r="B41" t="n">
-        <v>101571</v>
+        <v>93451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>671809</v>
+        <v>671949</v>
       </c>
       <c r="R41" t="n">
-        <v>6648285</v>
+        <v>6648020</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5130,7 +5089,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5140,7 +5099,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5166,38 +5125,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844348</t>
+          <t>https://artportalen.se/Sighting/136844361</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136844359</v>
+        <v>136975430</v>
       </c>
       <c r="B42" t="n">
-        <v>101571</v>
+        <v>93451</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5207,10 +5166,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672071</v>
+        <v>671947</v>
       </c>
       <c r="R42" t="n">
-        <v>6648085</v>
+        <v>6648018</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5237,22 +5196,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5267,49 +5226,49 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844359</t>
+          <t>https://artportalen.se/Sighting/136975430</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136844365</v>
+        <v>136975432</v>
       </c>
       <c r="B43" t="n">
-        <v>101571</v>
+        <v>93451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5319,10 +5278,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>671944</v>
+        <v>672011</v>
       </c>
       <c r="R43" t="n">
-        <v>6648126</v>
+        <v>6648066</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5349,22 +5308,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5379,18 +5338,4308 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136975432</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>136975436</v>
+      </c>
+      <c r="B44" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>672043</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6648077</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:58</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975436</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>136975439</v>
+      </c>
+      <c r="B45" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>672064</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6648093</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975439</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136975452</v>
+      </c>
+      <c r="B46" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>671811</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6648068</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975452</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>137064507</v>
+      </c>
+      <c r="B47" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>671946</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6648016</v>
+      </c>
+      <c r="S47" t="n">
+        <v>9</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064507</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>137064509</v>
+      </c>
+      <c r="B48" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>671985</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6648131</v>
+      </c>
+      <c r="S48" t="n">
+        <v>6</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064509</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>137064510</v>
+      </c>
+      <c r="B49" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>672002</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6648119</v>
+      </c>
+      <c r="S49" t="n">
+        <v>8</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064510</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>137064511</v>
+      </c>
+      <c r="B50" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>672003</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6648111</v>
+      </c>
+      <c r="S50" t="n">
+        <v>13</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064511</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137064516</v>
+      </c>
+      <c r="B51" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>671772</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6648263</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064516</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137074569</v>
+      </c>
+      <c r="B52" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>672079</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6648133</v>
+      </c>
+      <c r="S52" t="n">
+        <v>32</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074569</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137074576</v>
+      </c>
+      <c r="B53" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>672052</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6648073</v>
+      </c>
+      <c r="S53" t="n">
+        <v>16</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074576</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137074581</v>
+      </c>
+      <c r="B54" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>672029</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6648226</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074581</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>137074582</v>
+      </c>
+      <c r="B55" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>672023</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6648149</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074582</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>137074586</v>
+      </c>
+      <c r="B56" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>672005</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6648168</v>
+      </c>
+      <c r="S56" t="n">
+        <v>5</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074586</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>137074594</v>
+      </c>
+      <c r="B57" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>671987</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6648165</v>
+      </c>
+      <c r="S57" t="n">
+        <v>6</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074594</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>137074596</v>
+      </c>
+      <c r="B58" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>671979</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6648089</v>
+      </c>
+      <c r="S58" t="n">
+        <v>5</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074596</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>137074602</v>
+      </c>
+      <c r="B59" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>671915</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6648009</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074602</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>137074605</v>
+      </c>
+      <c r="B60" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>671905</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6647993</v>
+      </c>
+      <c r="S60" t="n">
+        <v>8</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074605</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>137074608</v>
+      </c>
+      <c r="B61" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>671871</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6648175</v>
+      </c>
+      <c r="S61" t="n">
+        <v>5</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074608</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>137074630</v>
+      </c>
+      <c r="B62" t="n">
+        <v>93451</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>671814</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6648075</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074630</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>137064518</v>
+      </c>
+      <c r="B63" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>671781</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6648217</v>
+      </c>
+      <c r="S63" t="n">
+        <v>8</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064518</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>137074635</v>
+      </c>
+      <c r="B64" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>671776</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6648211</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074635</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>137074634</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8452</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>671787</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6648164</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074634</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>137064515</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99384</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219862</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nästrot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Neottia nidus-avis</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>671859</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6648188</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064515</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136844366</v>
+      </c>
+      <c r="B67" t="n">
+        <v>107072</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>671939</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6648124</v>
+      </c>
+      <c r="S67" t="n">
+        <v>69</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844366</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>136844369</v>
+      </c>
+      <c r="B68" t="n">
+        <v>107072</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>671875</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6648159</v>
+      </c>
+      <c r="S68" t="n">
+        <v>9</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ej stora träd</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844369</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136844370</v>
+      </c>
+      <c r="B69" t="n">
+        <v>107072</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>671879</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6648093</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844370</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136844371</v>
+      </c>
+      <c r="B70" t="n">
+        <v>107072</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>671904</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6648132</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Litet träd</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844371</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136844368</v>
+      </c>
+      <c r="B71" t="n">
+        <v>104884</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>671875</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6648159</v>
+      </c>
+      <c r="S71" t="n">
+        <v>7</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844368</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136975429</v>
+      </c>
+      <c r="B72" t="n">
+        <v>104884</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>671936</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6648021</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975429</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>137064513</v>
+      </c>
+      <c r="B73" t="n">
+        <v>104884</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>671855</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6648166</v>
+      </c>
+      <c r="S73" t="n">
+        <v>6</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064513</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>137074607</v>
+      </c>
+      <c r="B74" t="n">
+        <v>104884</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>671884</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6647992</v>
+      </c>
+      <c r="S74" t="n">
+        <v>6</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074607</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136844348</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>671809</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6648285</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844348</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136844359</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>672071</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6648085</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844359</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136844365</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>671944</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6648126</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136844365</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>137074572</v>
+      </c>
+      <c r="B78" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>672063</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6648246</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074572</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>137074620</v>
+      </c>
+      <c r="B79" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>671830</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6648024</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074620</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>137074625</v>
+      </c>
+      <c r="B80" t="n">
+        <v>101571</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>671820</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6648296</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074625</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>137074615</v>
+      </c>
+      <c r="B81" t="n">
+        <v>87528</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>671855</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6648175</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074615</t>
         </is>
       </c>
     </row>
@@ -5438,6 +9687,44 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87504</v>
+        <v>87505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87429</v>
+        <v>87430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87594</v>
+        <v>87595</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87594</v>
+        <v>87595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87491</v>
+        <v>87492</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87491</v>
+        <v>87492</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87328</v>
+        <v>87329</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4351,7 +4351,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         <v>137064517</v>
       </c>
       <c r="B38" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>137074636</v>
       </c>
       <c r="B39" t="n">
-        <v>91624</v>
+        <v>91625</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>136844361</v>
       </c>
       <c r="B41" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136975430</v>
       </c>
       <c r="B42" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>136975432</v>
       </c>
       <c r="B43" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>136975436</v>
       </c>
       <c r="B44" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
         <v>136975439</v>
       </c>
       <c r="B45" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>136975452</v>
       </c>
       <c r="B46" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>137064507</v>
       </c>
       <c r="B47" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>137064509</v>
       </c>
       <c r="B48" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>137064510</v>
       </c>
       <c r="B49" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>137064511</v>
       </c>
       <c r="B50" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         <v>137064516</v>
       </c>
       <c r="B51" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>137074569</v>
       </c>
       <c r="B52" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>137074576</v>
       </c>
       <c r="B53" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>137074581</v>
       </c>
       <c r="B54" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6590,7 +6590,7 @@
         <v>137074582</v>
       </c>
       <c r="B55" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>137074586</v>
       </c>
       <c r="B56" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>137074594</v>
       </c>
       <c r="B57" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>137074596</v>
       </c>
       <c r="B58" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>137074602</v>
       </c>
       <c r="B59" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7150,7 +7150,7 @@
         <v>137074605</v>
       </c>
       <c r="B60" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7262,7 +7262,7 @@
         <v>137074608</v>
       </c>
       <c r="B61" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>137074630</v>
       </c>
       <c r="B62" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         <v>137064515</v>
       </c>
       <c r="B66" t="n">
-        <v>99384</v>
+        <v>99385</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>136844366</v>
       </c>
       <c r="B67" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>136844369</v>
       </c>
       <c r="B68" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>136844370</v>
       </c>
       <c r="B69" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>136844371</v>
       </c>
       <c r="B70" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>136844368</v>
       </c>
       <c r="B71" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8527,7 +8527,7 @@
         <v>136975429</v>
       </c>
       <c r="B72" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>137064513</v>
       </c>
       <c r="B73" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>137074607</v>
       </c>
       <c r="B74" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>136844348</v>
       </c>
       <c r="B75" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>136844359</v>
       </c>
       <c r="B76" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>136844365</v>
       </c>
       <c r="B77" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>137074572</v>
       </c>
       <c r="B78" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>137074620</v>
       </c>
       <c r="B79" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9423,7 +9423,7 @@
         <v>137074625</v>
       </c>
       <c r="B80" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>137074615</v>
       </c>
       <c r="B81" t="n">
-        <v>87528</v>
+        <v>87529</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ81"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2605,6 +2605,9 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
@@ -2665,6 +2668,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2676,10 +2680,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137064512</t>
@@ -3613,6 +3621,9 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
@@ -3673,6 +3684,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3684,10 +3696,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137064514</t>
@@ -4153,6 +4169,9 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
@@ -4213,6 +4232,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4224,10 +4244,14 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137064508</t>
@@ -4265,6 +4289,9 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
@@ -4325,6 +4352,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4336,10 +4364,14 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137064519</t>
@@ -4684,7 +4716,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137064517</v>
+        <v>137074636</v>
       </c>
       <c r="B38" t="n">
         <v>91625</v>
@@ -4715,17 +4747,17 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>671764</v>
+        <v>671767</v>
       </c>
       <c r="R38" t="n">
-        <v>6648252</v>
+        <v>6648247</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4754,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4764,7 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4779,65 +4811,65 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064517</t>
+          <t>https://artportalen.se/Sighting/137074636</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137074636</v>
+        <v>128262008</v>
       </c>
       <c r="B39" t="n">
-        <v>91625</v>
+        <v>91443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5747</v>
+        <v>5754</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>671767</v>
+        <v>671851</v>
       </c>
       <c r="R39" t="n">
-        <v>6648247</v>
+        <v>6648067</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4861,22 +4893,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:34</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4896,22 +4918,22 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074636</t>
+          <t>https://artportalen.se/Sighting/128262008</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128262008</v>
+        <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>91443</v>
+        <v>93452</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4919,37 +4941,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5754</v>
+        <v>5964</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>671851</v>
+        <v>671949</v>
       </c>
       <c r="R40" t="n">
-        <v>6648067</v>
+        <v>6648020</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4973,12 +5004,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4993,24 +5034,24 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128262008</t>
+          <t>https://artportalen.se/Sighting/136844361</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136844361</v>
+        <v>136975430</v>
       </c>
       <c r="B41" t="n">
         <v>93452</v>
@@ -5038,26 +5079,17 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>671949</v>
+        <v>671947</v>
       </c>
       <c r="R41" t="n">
-        <v>6648020</v>
+        <v>6648018</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5084,22 +5116,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5114,24 +5146,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844361</t>
+          <t>https://artportalen.se/Sighting/136975430</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136975430</v>
+        <v>136975432</v>
       </c>
       <c r="B42" t="n">
         <v>93452</v>
@@ -5166,10 +5198,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>671947</v>
+        <v>672011</v>
       </c>
       <c r="R42" t="n">
-        <v>6648018</v>
+        <v>6648066</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5201,7 +5233,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5211,7 +5243,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,13 +5269,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975430</t>
+          <t>https://artportalen.se/Sighting/136975432</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136975432</v>
+        <v>136975436</v>
       </c>
       <c r="B43" t="n">
         <v>93452</v>
@@ -5278,10 +5310,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672011</v>
+        <v>672043</v>
       </c>
       <c r="R43" t="n">
-        <v>6648066</v>
+        <v>6648077</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5313,7 +5345,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5323,7 +5355,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5349,13 +5381,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975432</t>
+          <t>https://artportalen.se/Sighting/136975436</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136975436</v>
+        <v>136975439</v>
       </c>
       <c r="B44" t="n">
         <v>93452</v>
@@ -5390,10 +5422,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672043</v>
+        <v>672064</v>
       </c>
       <c r="R44" t="n">
-        <v>6648077</v>
+        <v>6648093</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5425,7 +5457,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5435,7 +5467,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5461,13 +5493,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975436</t>
+          <t>https://artportalen.se/Sighting/136975439</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136975439</v>
+        <v>136975452</v>
       </c>
       <c r="B45" t="n">
         <v>93452</v>
@@ -5502,10 +5534,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672064</v>
+        <v>671811</v>
       </c>
       <c r="R45" t="n">
-        <v>6648093</v>
+        <v>6648068</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5537,7 +5569,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5547,7 +5579,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,13 +5605,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975439</t>
+          <t>https://artportalen.se/Sighting/136975452</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136975452</v>
+        <v>137064507</v>
       </c>
       <c r="B46" t="n">
         <v>93452</v>
@@ -5608,19 +5640,22 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>671811</v>
+        <v>671946</v>
       </c>
       <c r="R46" t="n">
-        <v>6648068</v>
+        <v>6648016</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5644,22 +5679,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5668,30 +5703,35 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975452</t>
+          <t>https://artportalen.se/Sighting/137064507</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137064507</v>
+        <v>137064509</v>
       </c>
       <c r="B47" t="n">
         <v>93452</v>
@@ -5720,19 +5760,22 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>671946</v>
+        <v>671985</v>
       </c>
       <c r="R47" t="n">
-        <v>6648016</v>
+        <v>6648131</v>
       </c>
       <c r="S47" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5761,7 +5804,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5771,7 +5814,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5780,6 +5823,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5791,19 +5835,23 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064507</t>
+          <t>https://artportalen.se/Sighting/137064509</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137064509</v>
+        <v>137064510</v>
       </c>
       <c r="B48" t="n">
         <v>93452</v>
@@ -5832,19 +5880,22 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>671985</v>
+        <v>672002</v>
       </c>
       <c r="R48" t="n">
-        <v>6648131</v>
+        <v>6648119</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5873,7 +5924,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5883,7 +5934,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5892,6 +5943,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5903,19 +5955,23 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064509</t>
+          <t>https://artportalen.se/Sighting/137064510</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137064510</v>
+        <v>137064511</v>
       </c>
       <c r="B49" t="n">
         <v>93452</v>
@@ -5944,19 +6000,22 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672002</v>
+        <v>672003</v>
       </c>
       <c r="R49" t="n">
-        <v>6648119</v>
+        <v>6648111</v>
       </c>
       <c r="S49" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5985,7 +6044,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5995,7 +6054,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6004,6 +6063,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6015,19 +6075,23 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064510</t>
+          <t>https://artportalen.se/Sighting/137064511</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137064511</v>
+        <v>137064516</v>
       </c>
       <c r="B50" t="n">
         <v>93452</v>
@@ -6056,19 +6120,22 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672003</v>
+        <v>671772</v>
       </c>
       <c r="R50" t="n">
-        <v>6648111</v>
+        <v>6648263</v>
       </c>
       <c r="S50" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6097,7 +6164,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6107,7 +6174,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6116,6 +6183,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6127,19 +6195,23 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064511</t>
+          <t>https://artportalen.se/Sighting/137064516</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137064516</v>
+        <v>137074569</v>
       </c>
       <c r="B51" t="n">
         <v>93452</v>
@@ -6170,17 +6242,17 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>671772</v>
+        <v>672079</v>
       </c>
       <c r="R51" t="n">
-        <v>6648263</v>
+        <v>6648133</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6209,7 +6281,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6219,7 +6291,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6234,24 +6306,24 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064516</t>
+          <t>https://artportalen.se/Sighting/137074569</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137074569</v>
+        <v>137074576</v>
       </c>
       <c r="B52" t="n">
         <v>93452</v>
@@ -6286,13 +6358,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672079</v>
+        <v>672052</v>
       </c>
       <c r="R52" t="n">
-        <v>6648133</v>
+        <v>6648073</v>
       </c>
       <c r="S52" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6321,7 +6393,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6331,7 +6403,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6357,13 +6429,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074569</t>
+          <t>https://artportalen.se/Sighting/137074576</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137074576</v>
+        <v>137074581</v>
       </c>
       <c r="B53" t="n">
         <v>93452</v>
@@ -6398,13 +6470,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672052</v>
+        <v>672029</v>
       </c>
       <c r="R53" t="n">
-        <v>6648073</v>
+        <v>6648226</v>
       </c>
       <c r="S53" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6433,7 +6505,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6443,7 +6515,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6469,13 +6541,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074576</t>
+          <t>https://artportalen.se/Sighting/137074581</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137074581</v>
+        <v>137074582</v>
       </c>
       <c r="B54" t="n">
         <v>93452</v>
@@ -6510,10 +6582,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672029</v>
+        <v>672023</v>
       </c>
       <c r="R54" t="n">
-        <v>6648226</v>
+        <v>6648149</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6545,7 +6617,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6555,7 +6627,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6581,13 +6653,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074581</t>
+          <t>https://artportalen.se/Sighting/137074582</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137074582</v>
+        <v>137074586</v>
       </c>
       <c r="B55" t="n">
         <v>93452</v>
@@ -6622,10 +6694,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672023</v>
+        <v>672005</v>
       </c>
       <c r="R55" t="n">
-        <v>6648149</v>
+        <v>6648168</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6657,7 +6729,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6667,7 +6739,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6693,13 +6765,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074582</t>
+          <t>https://artportalen.se/Sighting/137074586</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137074586</v>
+        <v>137074594</v>
       </c>
       <c r="B56" t="n">
         <v>93452</v>
@@ -6734,13 +6806,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672005</v>
+        <v>671987</v>
       </c>
       <c r="R56" t="n">
-        <v>6648168</v>
+        <v>6648165</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6769,7 +6841,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6779,7 +6851,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6805,13 +6877,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074586</t>
+          <t>https://artportalen.se/Sighting/137074594</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137074594</v>
+        <v>137074596</v>
       </c>
       <c r="B57" t="n">
         <v>93452</v>
@@ -6846,13 +6918,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>671987</v>
+        <v>671979</v>
       </c>
       <c r="R57" t="n">
-        <v>6648165</v>
+        <v>6648089</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6881,7 +6953,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6891,7 +6963,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6917,13 +6989,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074594</t>
+          <t>https://artportalen.se/Sighting/137074596</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137074596</v>
+        <v>137074602</v>
       </c>
       <c r="B58" t="n">
         <v>93452</v>
@@ -6958,10 +7030,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>671979</v>
+        <v>671915</v>
       </c>
       <c r="R58" t="n">
-        <v>6648089</v>
+        <v>6648009</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6993,7 +7065,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7003,7 +7075,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7029,13 +7101,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074596</t>
+          <t>https://artportalen.se/Sighting/137074602</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137074602</v>
+        <v>137074605</v>
       </c>
       <c r="B59" t="n">
         <v>93452</v>
@@ -7070,13 +7142,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>671915</v>
+        <v>671905</v>
       </c>
       <c r="R59" t="n">
-        <v>6648009</v>
+        <v>6647993</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7105,7 +7177,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7115,7 +7187,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7141,13 +7213,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074602</t>
+          <t>https://artportalen.se/Sighting/137074605</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137074605</v>
+        <v>137074608</v>
       </c>
       <c r="B60" t="n">
         <v>93452</v>
@@ -7182,13 +7254,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>671905</v>
+        <v>671871</v>
       </c>
       <c r="R60" t="n">
-        <v>6647993</v>
+        <v>6648175</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7217,7 +7289,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7227,7 +7299,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7253,13 +7325,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074605</t>
+          <t>https://artportalen.se/Sighting/137074608</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137074608</v>
+        <v>137074630</v>
       </c>
       <c r="B61" t="n">
         <v>93452</v>
@@ -7294,10 +7366,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>671871</v>
+        <v>671814</v>
       </c>
       <c r="R61" t="n">
-        <v>6648175</v>
+        <v>6648075</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7329,7 +7401,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7339,7 +7411,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7365,38 +7437,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074608</t>
+          <t>https://artportalen.se/Sighting/137074630</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137074630</v>
+        <v>137074635</v>
       </c>
       <c r="B62" t="n">
-        <v>93452</v>
+        <v>5182</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5964</v>
+        <v>100526</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7406,10 +7478,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>671814</v>
+        <v>671776</v>
       </c>
       <c r="R62" t="n">
-        <v>6648075</v>
+        <v>6648211</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -7441,7 +7513,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7451,7 +7523,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7477,16 +7549,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074630</t>
+          <t>https://artportalen.se/Sighting/137074635</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137064518</v>
+        <v>137074634</v>
       </c>
       <c r="B63" t="n">
-        <v>5182</v>
+        <v>8452</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7494,37 +7566,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>671781</v>
+        <v>671787</v>
       </c>
       <c r="R63" t="n">
-        <v>6648217</v>
+        <v>6648164</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7553,7 +7625,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7563,7 +7635,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7578,27 +7650,27 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064518</t>
+          <t>https://artportalen.se/Sighting/137074634</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137074635</v>
+        <v>137064515</v>
       </c>
       <c r="B64" t="n">
-        <v>5182</v>
+        <v>99385</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7606,37 +7678,41 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>219862</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>671776</v>
+        <v>671859</v>
       </c>
       <c r="R64" t="n">
-        <v>6648211</v>
+        <v>6648188</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7665,7 +7741,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7675,7 +7751,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7684,71 +7760,85 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074635</t>
+          <t>https://artportalen.se/Sighting/137064515</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137074634</v>
+        <v>136844366</v>
       </c>
       <c r="B65" t="n">
-        <v>8452</v>
+        <v>107073</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106554</v>
+        <v>220785</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>671787</v>
+        <v>671939</v>
       </c>
       <c r="R65" t="n">
-        <v>6648164</v>
+        <v>6648124</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7772,22 +7862,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7802,65 +7892,74 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074634</t>
+          <t>https://artportalen.se/Sighting/136844366</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137064515</v>
+        <v>136844369</v>
       </c>
       <c r="B66" t="n">
-        <v>99385</v>
+        <v>107073</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>219862</v>
+        <v>220785</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>671859</v>
+        <v>671875</v>
       </c>
       <c r="R66" t="n">
-        <v>6648188</v>
+        <v>6648159</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7884,22 +7983,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ej stora träd</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7914,24 +8018,24 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064515</t>
+          <t>https://artportalen.se/Sighting/136844369</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136844366</v>
+        <v>136844370</v>
       </c>
       <c r="B67" t="n">
         <v>107073</v>
@@ -7959,29 +8063,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>671939</v>
+        <v>671879</v>
       </c>
       <c r="R67" t="n">
-        <v>6648124</v>
+        <v>6648093</v>
       </c>
       <c r="S67" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8010,7 +8109,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8020,7 +8119,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8029,6 +8128,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8046,13 +8146,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844366</t>
+          <t>https://artportalen.se/Sighting/136844370</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136844369</v>
+        <v>136844371</v>
       </c>
       <c r="B68" t="n">
         <v>107073</v>
@@ -8080,29 +8180,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>671875</v>
+        <v>671904</v>
       </c>
       <c r="R68" t="n">
-        <v>6648159</v>
+        <v>6648132</v>
       </c>
       <c r="S68" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8131,7 +8222,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8141,12 +8232,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ej stora träd</t>
+          <t>Litet träd</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8172,33 +8263,33 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844369</t>
+          <t>https://artportalen.se/Sighting/136844371</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136844370</v>
+        <v>136844368</v>
       </c>
       <c r="B69" t="n">
-        <v>107073</v>
+        <v>104885</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8207,23 +8298,19 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>671879</v>
+        <v>671875</v>
       </c>
       <c r="R69" t="n">
-        <v>6648093</v>
+        <v>6648159</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8252,7 +8339,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8262,7 +8349,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8271,7 +8358,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8289,33 +8375,33 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844370</t>
+          <t>https://artportalen.se/Sighting/136844368</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136844371</v>
+        <v>136975429</v>
       </c>
       <c r="B70" t="n">
-        <v>107073</v>
+        <v>104885</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220785</v>
+        <v>222412</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8330,10 +8416,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>671904</v>
+        <v>671936</v>
       </c>
       <c r="R70" t="n">
-        <v>6648132</v>
+        <v>6648021</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8360,27 +8446,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Litet träd</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8395,24 +8476,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844371</t>
+          <t>https://artportalen.se/Sighting/136975429</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136844368</v>
+        <v>137064513</v>
       </c>
       <c r="B71" t="n">
         <v>104885</v>
@@ -8441,19 +8522,23 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>671875</v>
+        <v>671855</v>
       </c>
       <c r="R71" t="n">
-        <v>6648159</v>
+        <v>6648166</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8477,22 +8562,22 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8501,30 +8586,35 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844368</t>
+          <t>https://artportalen.se/Sighting/137064513</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136975429</v>
+        <v>137074607</v>
       </c>
       <c r="B72" t="n">
         <v>104885</v>
@@ -8555,17 +8645,17 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>671936</v>
+        <v>671884</v>
       </c>
       <c r="R72" t="n">
-        <v>6648021</v>
+        <v>6647992</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8589,22 +8679,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8624,22 +8714,22 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975429</t>
+          <t>https://artportalen.se/Sighting/137074607</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137064513</v>
+        <v>136844348</v>
       </c>
       <c r="B73" t="n">
-        <v>104885</v>
+        <v>101572</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8647,21 +8737,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8671,13 +8761,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>671855</v>
+        <v>671809</v>
       </c>
       <c r="R73" t="n">
-        <v>6648166</v>
+        <v>6648285</v>
       </c>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8701,22 +8791,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8731,27 +8821,27 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064513</t>
+          <t>https://artportalen.se/Sighting/136844348</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>137074607</v>
+        <v>136844359</v>
       </c>
       <c r="B74" t="n">
-        <v>104885</v>
+        <v>101572</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8759,37 +8849,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>671884</v>
+        <v>672071</v>
       </c>
       <c r="R74" t="n">
-        <v>6647992</v>
+        <v>6648085</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8813,22 +8903,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8843,24 +8933,24 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074607</t>
+          <t>https://artportalen.se/Sighting/136844359</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136844348</v>
+        <v>136844365</v>
       </c>
       <c r="B75" t="n">
         <v>101572</v>
@@ -8895,10 +8985,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>671809</v>
+        <v>671944</v>
       </c>
       <c r="R75" t="n">
-        <v>6648285</v>
+        <v>6648126</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8930,7 +9020,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8940,7 +9030,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8966,13 +9056,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844348</t>
+          <t>https://artportalen.se/Sighting/136844365</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136844359</v>
+        <v>137074572</v>
       </c>
       <c r="B76" t="n">
         <v>101572</v>
@@ -9003,14 +9093,14 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672071</v>
+        <v>672063</v>
       </c>
       <c r="R76" t="n">
-        <v>6648085</v>
+        <v>6648246</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9037,22 +9127,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9067,24 +9157,24 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844359</t>
+          <t>https://artportalen.se/Sighting/137074572</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136844365</v>
+        <v>137074620</v>
       </c>
       <c r="B77" t="n">
         <v>101572</v>
@@ -9115,14 +9205,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>671944</v>
+        <v>671830</v>
       </c>
       <c r="R77" t="n">
-        <v>6648126</v>
+        <v>6648024</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9149,22 +9239,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9179,24 +9269,24 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844365</t>
+          <t>https://artportalen.se/Sighting/137074620</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137074572</v>
+        <v>137074625</v>
       </c>
       <c r="B78" t="n">
         <v>101572</v>
@@ -9231,10 +9321,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672063</v>
+        <v>671820</v>
       </c>
       <c r="R78" t="n">
-        <v>6648246</v>
+        <v>6648296</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9266,7 +9356,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9276,7 +9366,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9302,38 +9392,38 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074572</t>
+          <t>https://artportalen.se/Sighting/137074625</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137074620</v>
+        <v>137074615</v>
       </c>
       <c r="B79" t="n">
-        <v>101572</v>
+        <v>87529</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222498</v>
+        <v>6003295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Odörspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cortinarius russeoides</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>M.M.Moser</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9343,10 +9433,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>671830</v>
+        <v>671855</v>
       </c>
       <c r="R79" t="n">
-        <v>6648024</v>
+        <v>6648175</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9378,7 +9468,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9388,7 +9478,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9397,6 +9487,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9413,231 +9504,6 @@
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137074620</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>137074625</v>
-      </c>
-      <c r="B80" t="n">
-        <v>101572</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>hammarbol, Upl</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>671820</v>
-      </c>
-      <c r="R80" t="n">
-        <v>6648296</v>
-      </c>
-      <c r="S80" t="n">
-        <v>5</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Almunge</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/137074625</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>137074615</v>
-      </c>
-      <c r="B81" t="n">
-        <v>87529</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>6003295</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Odörspindling</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Cortinarius russeoides</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>hammarbol, Upl</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>671855</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6648175</v>
-      </c>
-      <c r="S81" t="n">
-        <v>5</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Almunge</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF81" t="inlineStr"/>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
-      <c r="AZ81" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137074615</t>
         </is>
@@ -9723,8 +9589,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87505</v>
+        <v>87511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87430</v>
+        <v>87436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87595</v>
+        <v>87601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87595</v>
+        <v>87601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87492</v>
+        <v>87498</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87329</v>
+        <v>87335</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93412</v>
+        <v>93418</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93412</v>
+        <v>93418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91625</v>
+        <v>91631</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>137064515</v>
       </c>
       <c r="B64" t="n">
-        <v>99385</v>
+        <v>99391</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136844366</v>
       </c>
       <c r="B65" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>136844369</v>
       </c>
       <c r="B66" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136844370</v>
       </c>
       <c r="B67" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>136844371</v>
       </c>
       <c r="B68" t="n">
-        <v>107073</v>
+        <v>107079</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>136844368</v>
       </c>
       <c r="B69" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>136975429</v>
       </c>
       <c r="B70" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>137064513</v>
       </c>
       <c r="B71" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>137074607</v>
       </c>
       <c r="B72" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>136844348</v>
       </c>
       <c r="B73" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>136844359</v>
       </c>
       <c r="B74" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>136844365</v>
       </c>
       <c r="B75" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>137074572</v>
       </c>
       <c r="B76" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>137074620</v>
       </c>
       <c r="B77" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>137074625</v>
       </c>
       <c r="B78" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>137074615</v>
       </c>
       <c r="B79" t="n">
-        <v>87529</v>
+        <v>87535</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87511</v>
+        <v>87515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87436</v>
+        <v>87440</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87601</v>
+        <v>87605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87601</v>
+        <v>87605</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87335</v>
+        <v>87339</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93418</v>
+        <v>93422</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93418</v>
+        <v>93422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91605</v>
+        <v>91609</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91631</v>
+        <v>91635</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>137064515</v>
       </c>
       <c r="B64" t="n">
-        <v>99391</v>
+        <v>99395</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136844366</v>
       </c>
       <c r="B65" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>136844369</v>
       </c>
       <c r="B66" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136844370</v>
       </c>
       <c r="B67" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>136844371</v>
       </c>
       <c r="B68" t="n">
-        <v>107079</v>
+        <v>107083</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>136844368</v>
       </c>
       <c r="B69" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>136975429</v>
       </c>
       <c r="B70" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>137064513</v>
       </c>
       <c r="B71" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>137074607</v>
       </c>
       <c r="B72" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>136844348</v>
       </c>
       <c r="B73" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>136844359</v>
       </c>
       <c r="B74" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>136844365</v>
       </c>
       <c r="B75" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>137074572</v>
       </c>
       <c r="B76" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>137074620</v>
       </c>
       <c r="B77" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>137074625</v>
       </c>
       <c r="B78" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>137074615</v>
       </c>
       <c r="B79" t="n">
-        <v>87535</v>
+        <v>87539</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
@@ -7670,7 +7670,7 @@
         <v>137064515</v>
       </c>
       <c r="B64" t="n">
-        <v>99395</v>
+        <v>99397</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136844366</v>
       </c>
       <c r="B65" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>136844369</v>
       </c>
       <c r="B66" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136844370</v>
       </c>
       <c r="B67" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>136844371</v>
       </c>
       <c r="B68" t="n">
-        <v>107083</v>
+        <v>107085</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>136844368</v>
       </c>
       <c r="B69" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>136975429</v>
       </c>
       <c r="B70" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>137064513</v>
       </c>
       <c r="B71" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>137074607</v>
       </c>
       <c r="B72" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>136844348</v>
       </c>
       <c r="B73" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>136844359</v>
       </c>
       <c r="B74" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>136844365</v>
       </c>
       <c r="B75" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>137074572</v>
       </c>
       <c r="B76" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>137074620</v>
       </c>
       <c r="B77" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>137074625</v>
       </c>
       <c r="B78" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87515</v>
+        <v>87517</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87440</v>
+        <v>87442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87605</v>
+        <v>87607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87605</v>
+        <v>87607</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87339</v>
+        <v>87341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93422</v>
+        <v>93424</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93422</v>
+        <v>93424</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91635</v>
+        <v>91637</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>137064515</v>
       </c>
       <c r="B64" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136844366</v>
       </c>
       <c r="B65" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>136844369</v>
       </c>
       <c r="B66" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136844370</v>
       </c>
       <c r="B67" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>136844371</v>
       </c>
       <c r="B68" t="n">
-        <v>107085</v>
+        <v>107087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>136844368</v>
       </c>
       <c r="B69" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>136975429</v>
       </c>
       <c r="B70" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>137064513</v>
       </c>
       <c r="B71" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>137074607</v>
       </c>
       <c r="B72" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>136844348</v>
       </c>
       <c r="B73" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>136844359</v>
       </c>
       <c r="B74" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>136844365</v>
       </c>
       <c r="B75" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>137074572</v>
       </c>
       <c r="B76" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>137074620</v>
       </c>
       <c r="B77" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>137074625</v>
       </c>
       <c r="B78" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>137074615</v>
       </c>
       <c r="B79" t="n">
-        <v>87539</v>
+        <v>87541</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87517</v>
+        <v>87530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87442</v>
+        <v>87455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87607</v>
+        <v>87620</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87607</v>
+        <v>87620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87341</v>
+        <v>87354</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93424</v>
+        <v>93437</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93424</v>
+        <v>93437</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91611</v>
+        <v>91624</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91637</v>
+        <v>91650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Tomas Falk, Gustav Bringby, Nina Tadsen</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>137064515</v>
       </c>
       <c r="B64" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136844366</v>
       </c>
       <c r="B65" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>136844369</v>
       </c>
       <c r="B66" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>136844370</v>
       </c>
       <c r="B67" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>136844371</v>
       </c>
       <c r="B68" t="n">
-        <v>107087</v>
+        <v>107100</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>136844368</v>
       </c>
       <c r="B69" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         <v>136975429</v>
       </c>
       <c r="B70" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>137064513</v>
       </c>
       <c r="B71" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>137074607</v>
       </c>
       <c r="B72" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>136844348</v>
       </c>
       <c r="B73" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8841,7 +8841,7 @@
         <v>136844359</v>
       </c>
       <c r="B74" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>136844365</v>
       </c>
       <c r="B75" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>137074572</v>
       </c>
       <c r="B76" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>137074620</v>
       </c>
       <c r="B77" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>137074625</v>
       </c>
       <c r="B78" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         <v>137074615</v>
       </c>
       <c r="B79" t="n">
-        <v>87541</v>
+        <v>87554</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ79"/>
+  <dimension ref="A1:AZ89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87530</v>
+        <v>87532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87455</v>
+        <v>87457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87620</v>
+        <v>87622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87620</v>
+        <v>87622</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87354</v>
+        <v>87356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93437</v>
+        <v>93438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93437</v>
+        <v>93438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91650</v>
+        <v>91652</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,48 +7443,59 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137074635</v>
+        <v>137249194</v>
       </c>
       <c r="B62" t="n">
-        <v>5182</v>
+        <v>93478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>671776</v>
+        <v>672003</v>
       </c>
       <c r="R62" t="n">
-        <v>6648211</v>
+        <v>6648067</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7513,7 +7524,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7523,7 +7534,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Många i en ring</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7532,71 +7548,87 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074635</t>
+          <t>https://artportalen.se/Sighting/137249194</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137074634</v>
+        <v>137249195</v>
       </c>
       <c r="B63" t="n">
-        <v>8452</v>
+        <v>93478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>671787</v>
+        <v>672048</v>
       </c>
       <c r="R63" t="n">
-        <v>6648164</v>
+        <v>6648057</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7625,7 +7657,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7635,7 +7667,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ring</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7644,61 +7681,73 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074634</t>
+          <t>https://artportalen.se/Sighting/137249195</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137064515</v>
+        <v>137249196</v>
       </c>
       <c r="B64" t="n">
-        <v>99412</v>
+        <v>93478</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219862</v>
+        <v>5964</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7706,13 +7755,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>671859</v>
+        <v>672056</v>
       </c>
       <c r="R64" t="n">
-        <v>6648188</v>
+        <v>6648064</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7741,7 +7790,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7751,7 +7800,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Stor ring</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7767,12 +7821,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7782,38 +7836,38 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064515</t>
+          <t>https://artportalen.se/Sighting/137249196</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136844366</v>
+        <v>137249197</v>
       </c>
       <c r="B65" t="n">
-        <v>107100</v>
+        <v>93478</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -7823,22 +7877,24 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>671939</v>
+        <v>672057</v>
       </c>
       <c r="R65" t="n">
-        <v>6648124</v>
+        <v>6648104</v>
       </c>
       <c r="S65" t="n">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7862,22 +7918,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7886,80 +7942,87 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844366</t>
+          <t>https://artportalen.se/Sighting/137249197</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136844369</v>
+        <v>137249198</v>
       </c>
       <c r="B66" t="n">
-        <v>107100</v>
+        <v>93478</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>671875</v>
+        <v>672062</v>
       </c>
       <c r="R66" t="n">
-        <v>6648159</v>
+        <v>6648106</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7983,27 +8046,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ej stora träd</t>
+          <t>På rad</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8012,61 +8075,73 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY66" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844369</t>
+          <t>https://artportalen.se/Sighting/137249198</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136844370</v>
+        <v>137249199</v>
       </c>
       <c r="B67" t="n">
-        <v>107100</v>
+        <v>93478</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8074,13 +8149,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>671879</v>
+        <v>672047</v>
       </c>
       <c r="R67" t="n">
-        <v>6648093</v>
+        <v>6648144</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8104,22 +8179,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8135,65 +8210,80 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY67" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844370</t>
+          <t>https://artportalen.se/Sighting/137249199</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136844371</v>
+        <v>137249200</v>
       </c>
       <c r="B68" t="n">
-        <v>107100</v>
+        <v>93478</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220785</v>
+        <v>5964</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>671904</v>
+        <v>671941</v>
       </c>
       <c r="R68" t="n">
-        <v>6648132</v>
+        <v>6648170</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8217,27 +8307,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Litet träd</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8246,71 +8331,87 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844371</t>
+          <t>https://artportalen.se/Sighting/137249200</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136844368</v>
+        <v>137249203</v>
       </c>
       <c r="B69" t="n">
-        <v>104912</v>
+        <v>93478</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>671875</v>
+        <v>671819</v>
       </c>
       <c r="R69" t="n">
-        <v>6648159</v>
+        <v>6648202</v>
       </c>
       <c r="S69" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8334,22 +8435,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Rad</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8358,71 +8464,87 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844368</t>
+          <t>https://artportalen.se/Sighting/137249203</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136975429</v>
+        <v>137249205</v>
       </c>
       <c r="B70" t="n">
-        <v>104912</v>
+        <v>93478</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>671936</v>
+        <v>671781</v>
       </c>
       <c r="R70" t="n">
-        <v>6648021</v>
+        <v>6648258</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8446,22 +8568,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8470,61 +8592,73 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975429</t>
+          <t>https://artportalen.se/Sighting/137249205</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>137064513</v>
+        <v>137249206</v>
       </c>
       <c r="B71" t="n">
-        <v>104912</v>
+        <v>93478</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222412</v>
+        <v>5964</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -8532,13 +8666,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>671855</v>
+        <v>671771</v>
       </c>
       <c r="R71" t="n">
-        <v>6648166</v>
+        <v>6648209</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8567,7 +8701,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8577,7 +8711,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8593,12 +8727,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -8608,16 +8742,16 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064513</t>
+          <t>https://artportalen.se/Sighting/137249206</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137074607</v>
+        <v>137074635</v>
       </c>
       <c r="B72" t="n">
-        <v>104912</v>
+        <v>5182</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8625,21 +8759,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222412</v>
+        <v>100526</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8649,13 +8783,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>671884</v>
+        <v>671776</v>
       </c>
       <c r="R72" t="n">
-        <v>6647992</v>
+        <v>6648211</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8684,7 +8818,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8694,7 +8828,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8720,16 +8854,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074607</t>
+          <t>https://artportalen.se/Sighting/137074635</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136844348</v>
+        <v>137074634</v>
       </c>
       <c r="B73" t="n">
-        <v>101599</v>
+        <v>8453</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8737,34 +8871,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>106554</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>671809</v>
+        <v>671787</v>
       </c>
       <c r="R73" t="n">
-        <v>6648285</v>
+        <v>6648164</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8791,22 +8925,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8821,27 +8955,27 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844348</t>
+          <t>https://artportalen.se/Sighting/137074634</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136844359</v>
+        <v>137064515</v>
       </c>
       <c r="B74" t="n">
-        <v>101599</v>
+        <v>99414</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8849,37 +8983,41 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672071</v>
+        <v>671859</v>
       </c>
       <c r="R74" t="n">
-        <v>6648085</v>
+        <v>6648188</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8903,22 +9041,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8927,71 +9065,85 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844359</t>
+          <t>https://artportalen.se/Sighting/137064515</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136844365</v>
+        <v>136844366</v>
       </c>
       <c r="B75" t="n">
-        <v>101599</v>
+        <v>107102</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>671944</v>
+        <v>671939</v>
       </c>
       <c r="R75" t="n">
-        <v>6648126</v>
+        <v>6648124</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9020,7 +9172,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9030,7 +9182,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9056,54 +9208,63 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844365</t>
+          <t>https://artportalen.se/Sighting/136844366</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>137074572</v>
+        <v>136844369</v>
       </c>
       <c r="B76" t="n">
-        <v>101599</v>
+        <v>107102</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672063</v>
+        <v>671875</v>
       </c>
       <c r="R76" t="n">
-        <v>6648246</v>
+        <v>6648159</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9127,22 +9288,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ej stora träd</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9157,62 +9323,66 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074572</t>
+          <t>https://artportalen.se/Sighting/136844369</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>137074620</v>
+        <v>136844370</v>
       </c>
       <c r="B77" t="n">
-        <v>101599</v>
+        <v>107102</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>671830</v>
+        <v>671879</v>
       </c>
       <c r="R77" t="n">
-        <v>6648024</v>
+        <v>6648093</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9239,22 +9409,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9263,68 +9433,69 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074620</t>
+          <t>https://artportalen.se/Sighting/136844370</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>137074625</v>
+        <v>136844371</v>
       </c>
       <c r="B78" t="n">
-        <v>101599</v>
+        <v>107102</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>222498</v>
+        <v>220785</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>671820</v>
+        <v>671904</v>
       </c>
       <c r="R78" t="n">
-        <v>6648296</v>
+        <v>6648132</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9351,22 +9522,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Litet träd</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9381,65 +9557,65 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074625</t>
+          <t>https://artportalen.se/Sighting/136844371</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>137074615</v>
+        <v>136844368</v>
       </c>
       <c r="B79" t="n">
-        <v>87554</v>
+        <v>104914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6003295</v>
+        <v>222412</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>671855</v>
+        <v>671875</v>
       </c>
       <c r="R79" t="n">
-        <v>6648175</v>
+        <v>6648159</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9463,22 +9639,22 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9487,23 +9663,1152 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844368</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>136975429</v>
+      </c>
+      <c r="B80" t="n">
+        <v>104914</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>671936</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6648021</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136975429</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>137064513</v>
+      </c>
+      <c r="B81" t="n">
+        <v>104914</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>671855</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6648166</v>
+      </c>
+      <c r="S81" t="n">
+        <v>6</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Nina Tadsen</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137064513</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>137074607</v>
+      </c>
+      <c r="B82" t="n">
+        <v>104914</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>671884</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6647992</v>
+      </c>
+      <c r="S82" t="n">
+        <v>6</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074607</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>136844348</v>
+      </c>
+      <c r="B83" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>671809</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6648285</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844348</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>136844359</v>
+      </c>
+      <c r="B84" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>672071</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6648085</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844359</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>136844365</v>
+      </c>
+      <c r="B85" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>671944</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6648126</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136844365</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>137074572</v>
+      </c>
+      <c r="B86" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>672063</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6648246</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:36</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074572</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>137074620</v>
+      </c>
+      <c r="B87" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>671830</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6648024</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074620</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>137074625</v>
+      </c>
+      <c r="B88" t="n">
+        <v>101601</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>671820</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6648296</v>
+      </c>
+      <c r="S88" t="n">
+        <v>5</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074625</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>137074615</v>
+      </c>
+      <c r="B89" t="n">
+        <v>87556</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>671855</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6648175</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137074615</t>
         </is>
@@ -9589,6 +10894,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87532</v>
+        <v>87535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87457</v>
+        <v>87460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87622</v>
+        <v>87625</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87622</v>
+        <v>87625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87356</v>
+        <v>87359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91626</v>
+        <v>91629</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91652</v>
+        <v>91655</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137249194</v>
       </c>
       <c r="B62" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7579,7 +7579,7 @@
         <v>137249195</v>
       </c>
       <c r="B63" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7712,7 +7712,7 @@
         <v>137249196</v>
       </c>
       <c r="B64" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7845,7 +7845,7 @@
         <v>137249197</v>
       </c>
       <c r="B65" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         <v>137249198</v>
       </c>
       <c r="B66" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>137249199</v>
       </c>
       <c r="B67" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         <v>137249200</v>
       </c>
       <c r="B68" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>137249203</v>
       </c>
       <c r="B69" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>137249205</v>
       </c>
       <c r="B70" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         <v>137249206</v>
       </c>
       <c r="B71" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137064515</v>
       </c>
       <c r="B74" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>136844366</v>
       </c>
       <c r="B75" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>136844369</v>
       </c>
       <c r="B76" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         <v>136844370</v>
       </c>
       <c r="B77" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>136844371</v>
       </c>
       <c r="B78" t="n">
-        <v>107102</v>
+        <v>107106</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
         <v>136844368</v>
       </c>
       <c r="B79" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>136975429</v>
       </c>
       <c r="B80" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         <v>137064513</v>
       </c>
       <c r="B81" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9922,7 +9922,7 @@
         <v>137074607</v>
       </c>
       <c r="B82" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>136844348</v>
       </c>
       <c r="B83" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10146,7 +10146,7 @@
         <v>136844359</v>
       </c>
       <c r="B84" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>136844365</v>
       </c>
       <c r="B85" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>137074572</v>
       </c>
       <c r="B86" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>137074620</v>
       </c>
       <c r="B87" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>137074625</v>
       </c>
       <c r="B88" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>137074615</v>
       </c>
       <c r="B89" t="n">
-        <v>87556</v>
+        <v>87559</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ89"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87535</v>
+        <v>87545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87460</v>
+        <v>87470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87625</v>
+        <v>87635</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87625</v>
+        <v>87635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87359</v>
+        <v>87369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93441</v>
+        <v>93451</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93441</v>
+        <v>93451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91629</v>
+        <v>91639</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91655</v>
+        <v>91665</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137249194</v>
+        <v>137249193</v>
       </c>
       <c r="B62" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7473,29 +7473,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672003</v>
+        <v>671957</v>
       </c>
       <c r="R62" t="n">
-        <v>6648067</v>
+        <v>6648013</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7524,7 +7522,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7534,7 +7532,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7548,7 +7546,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7563,23 +7560,19 @@
           <t>Gustav Bringby</t>
         </is>
       </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+      <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249194</t>
+          <t>https://artportalen.se/Sighting/137249193</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137249195</v>
+        <v>137249194</v>
       </c>
       <c r="B63" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7606,7 +7599,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7622,13 +7615,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672048</v>
+        <v>672003</v>
       </c>
       <c r="R63" t="n">
-        <v>6648057</v>
+        <v>6648067</v>
       </c>
       <c r="S63" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7657,7 +7650,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7667,12 +7660,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ring</t>
+          <t>Många i en ring</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7703,16 +7696,16 @@
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249195</t>
+          <t>https://artportalen.se/Sighting/137249194</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137249196</v>
+        <v>137249195</v>
       </c>
       <c r="B64" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7739,7 +7732,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7755,13 +7748,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672056</v>
+        <v>672048</v>
       </c>
       <c r="R64" t="n">
-        <v>6648064</v>
+        <v>6648057</v>
       </c>
       <c r="S64" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7790,7 +7783,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7800,12 +7793,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Stor ring</t>
+          <t>Ring</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7836,16 +7829,16 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249196</t>
+          <t>https://artportalen.se/Sighting/137249195</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137249197</v>
+        <v>137249196</v>
       </c>
       <c r="B65" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7872,7 +7865,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7888,13 +7881,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672057</v>
+        <v>672056</v>
       </c>
       <c r="R65" t="n">
-        <v>6648104</v>
+        <v>6648064</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7923,7 +7916,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7933,7 +7926,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Stor ring</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7964,16 +7962,16 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249197</t>
+          <t>https://artportalen.se/Sighting/137249196</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137249198</v>
+        <v>137249197</v>
       </c>
       <c r="B66" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8000,7 +7998,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8016,13 +8014,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672062</v>
+        <v>672057</v>
       </c>
       <c r="R66" t="n">
-        <v>6648106</v>
+        <v>6648104</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8051,7 +8049,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8061,12 +8059,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På rad</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8097,16 +8090,16 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249198</t>
+          <t>https://artportalen.se/Sighting/137249197</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>137249199</v>
+        <v>137249198</v>
       </c>
       <c r="B67" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8133,7 +8126,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8149,13 +8142,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672047</v>
+        <v>672062</v>
       </c>
       <c r="R67" t="n">
-        <v>6648144</v>
+        <v>6648106</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8184,7 +8177,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8194,7 +8187,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På rad</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8225,16 +8223,16 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249199</t>
+          <t>https://artportalen.se/Sighting/137249198</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137249200</v>
+        <v>137249199</v>
       </c>
       <c r="B68" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8261,7 +8259,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8277,13 +8275,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>671941</v>
+        <v>672047</v>
       </c>
       <c r="R68" t="n">
-        <v>6648170</v>
+        <v>6648144</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8312,7 +8310,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8322,7 +8320,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8353,16 +8351,16 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249200</t>
+          <t>https://artportalen.se/Sighting/137249199</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137249203</v>
+        <v>137249200</v>
       </c>
       <c r="B69" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8389,7 +8387,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8405,13 +8403,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>671819</v>
+        <v>671941</v>
       </c>
       <c r="R69" t="n">
-        <v>6648202</v>
+        <v>6648170</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8440,7 +8438,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8450,12 +8448,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Rad</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8486,16 +8479,16 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249203</t>
+          <t>https://artportalen.se/Sighting/137249200</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>137249205</v>
+        <v>137249201</v>
       </c>
       <c r="B70" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8522,7 +8515,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8538,13 +8531,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>671781</v>
+        <v>671896</v>
       </c>
       <c r="R70" t="n">
-        <v>6648258</v>
+        <v>6648164</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8573,7 +8566,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8583,7 +8576,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ring</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8614,16 +8612,16 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249205</t>
+          <t>https://artportalen.se/Sighting/137249201</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>137249206</v>
+        <v>137249203</v>
       </c>
       <c r="B71" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8650,7 +8648,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8666,13 +8664,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>671771</v>
+        <v>671819</v>
       </c>
       <c r="R71" t="n">
-        <v>6648209</v>
+        <v>6648202</v>
       </c>
       <c r="S71" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8701,7 +8699,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8711,7 +8709,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Rad</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8742,54 +8745,65 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249206</t>
+          <t>https://artportalen.se/Sighting/137249203</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137074635</v>
+        <v>137249205</v>
       </c>
       <c r="B72" t="n">
-        <v>5182</v>
+        <v>93491</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>671776</v>
+        <v>671781</v>
       </c>
       <c r="R72" t="n">
-        <v>6648211</v>
+        <v>6648258</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8818,7 +8832,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8828,7 +8842,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8837,71 +8851,87 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074635</t>
+          <t>https://artportalen.se/Sighting/137249205</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137074634</v>
+        <v>137249206</v>
       </c>
       <c r="B73" t="n">
-        <v>8453</v>
+        <v>93491</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106554</v>
+        <v>5964</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>671787</v>
+        <v>671771</v>
       </c>
       <c r="R73" t="n">
-        <v>6648164</v>
+        <v>6648209</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8930,7 +8960,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8940,7 +8970,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8949,33 +8979,38 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074634</t>
+          <t>https://artportalen.se/Sighting/137249206</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>137064515</v>
+        <v>137074635</v>
       </c>
       <c r="B74" t="n">
-        <v>99417</v>
+        <v>5188</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8983,41 +9018,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>219862</v>
+        <v>100526</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>671859</v>
+        <v>671776</v>
       </c>
       <c r="R74" t="n">
-        <v>6648188</v>
+        <v>6648211</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9046,7 +9077,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9056,7 +9087,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9065,85 +9096,71 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064515</t>
+          <t>https://artportalen.se/Sighting/137074635</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136844366</v>
+        <v>137074634</v>
       </c>
       <c r="B75" t="n">
-        <v>107106</v>
+        <v>8459</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220785</v>
+        <v>106554</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>671939</v>
+        <v>671787</v>
       </c>
       <c r="R75" t="n">
-        <v>6648124</v>
+        <v>6648164</v>
       </c>
       <c r="S75" t="n">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9167,22 +9184,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9197,74 +9214,69 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844366</t>
+          <t>https://artportalen.se/Sighting/137074634</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136844369</v>
+        <v>137064515</v>
       </c>
       <c r="B76" t="n">
-        <v>107106</v>
+        <v>99427</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>671875</v>
+        <v>671859</v>
       </c>
       <c r="R76" t="n">
-        <v>6648159</v>
+        <v>6648188</v>
       </c>
       <c r="S76" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9288,27 +9300,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ej stora träd</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9317,33 +9324,38 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844369</t>
+          <t>https://artportalen.se/Sighting/137064515</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136844370</v>
+        <v>136844366</v>
       </c>
       <c r="B77" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9368,24 +9380,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>671879</v>
+        <v>671939</v>
       </c>
       <c r="R77" t="n">
-        <v>6648093</v>
+        <v>6648124</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9414,7 +9431,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9424,7 +9441,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9433,7 +9450,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9451,16 +9467,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844370</t>
+          <t>https://artportalen.se/Sighting/136844366</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136844371</v>
+        <v>136844369</v>
       </c>
       <c r="B78" t="n">
-        <v>107106</v>
+        <v>107126</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9485,20 +9501,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>671904</v>
+        <v>671875</v>
       </c>
       <c r="R78" t="n">
-        <v>6648132</v>
+        <v>6648159</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9527,7 +9552,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9537,12 +9562,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Litet träd</t>
+          <t>Ej stora träd</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9568,33 +9593,33 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844371</t>
+          <t>https://artportalen.se/Sighting/136844369</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136844368</v>
+        <v>136844370</v>
       </c>
       <c r="B79" t="n">
-        <v>104917</v>
+        <v>107126</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9603,19 +9628,23 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>671875</v>
+        <v>671879</v>
       </c>
       <c r="R79" t="n">
-        <v>6648159</v>
+        <v>6648093</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9644,7 +9673,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9654,7 +9683,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9663,6 +9692,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9680,33 +9710,33 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844368</t>
+          <t>https://artportalen.se/Sighting/136844370</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136975429</v>
+        <v>136844371</v>
       </c>
       <c r="B80" t="n">
-        <v>104917</v>
+        <v>107126</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9721,10 +9751,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>671936</v>
+        <v>671904</v>
       </c>
       <c r="R80" t="n">
-        <v>6648021</v>
+        <v>6648132</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9751,22 +9781,27 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Litet träd</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9781,27 +9816,27 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975429</t>
+          <t>https://artportalen.se/Sighting/136844371</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>137064513</v>
+        <v>136844368</v>
       </c>
       <c r="B81" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9827,23 +9862,19 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>671855</v>
+        <v>671875</v>
       </c>
       <c r="R81" t="n">
-        <v>6648166</v>
+        <v>6648159</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9867,22 +9898,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9891,38 +9922,33 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064513</t>
+          <t>https://artportalen.se/Sighting/136844368</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>137074607</v>
+        <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9950,17 +9976,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>671884</v>
+        <v>671936</v>
       </c>
       <c r="R82" t="n">
-        <v>6647992</v>
+        <v>6648021</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9984,22 +10010,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10019,22 +10045,22 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074607</t>
+          <t>https://artportalen.se/Sighting/136975429</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136844348</v>
+        <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>101604</v>
+        <v>104936</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10042,37 +10068,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>671809</v>
+        <v>671855</v>
       </c>
       <c r="R83" t="n">
-        <v>6648285</v>
+        <v>6648166</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10096,22 +10126,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10120,33 +10150,38 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr"/>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844348</t>
+          <t>https://artportalen.se/Sighting/137064513</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136844359</v>
+        <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>101604</v>
+        <v>104936</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10154,37 +10189,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672071</v>
+        <v>671884</v>
       </c>
       <c r="R84" t="n">
-        <v>6648085</v>
+        <v>6647992</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10208,22 +10243,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10238,27 +10273,27 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844359</t>
+          <t>https://artportalen.se/Sighting/137074607</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136844365</v>
+        <v>136844348</v>
       </c>
       <c r="B85" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10290,10 +10325,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>671944</v>
+        <v>671809</v>
       </c>
       <c r="R85" t="n">
-        <v>6648126</v>
+        <v>6648285</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10325,7 +10360,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10335,7 +10370,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10361,16 +10396,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844365</t>
+          <t>https://artportalen.se/Sighting/136844348</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>137074572</v>
+        <v>136844359</v>
       </c>
       <c r="B86" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10398,14 +10433,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672063</v>
+        <v>672071</v>
       </c>
       <c r="R86" t="n">
-        <v>6648246</v>
+        <v>6648085</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10432,22 +10467,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10462,27 +10497,27 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074572</t>
+          <t>https://artportalen.se/Sighting/136844359</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>137074620</v>
+        <v>136844365</v>
       </c>
       <c r="B87" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10510,14 +10545,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>671830</v>
+        <v>671944</v>
       </c>
       <c r="R87" t="n">
-        <v>6648024</v>
+        <v>6648126</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10544,22 +10579,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10574,27 +10609,27 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074620</t>
+          <t>https://artportalen.se/Sighting/136844365</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>137074625</v>
+        <v>137074572</v>
       </c>
       <c r="B88" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10626,10 +10661,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>671820</v>
+        <v>672063</v>
       </c>
       <c r="R88" t="n">
-        <v>6648296</v>
+        <v>6648246</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10661,7 +10696,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10671,7 +10706,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10697,38 +10732,38 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074625</t>
+          <t>https://artportalen.se/Sighting/137074572</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>137074615</v>
+        <v>137074620</v>
       </c>
       <c r="B89" t="n">
-        <v>87559</v>
+        <v>101619</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10738,10 +10773,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>671855</v>
+        <v>671830</v>
       </c>
       <c r="R89" t="n">
-        <v>6648175</v>
+        <v>6648024</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10773,7 +10808,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10783,7 +10818,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10792,7 +10827,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10809,6 +10843,231 @@
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074620</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>137074625</v>
+      </c>
+      <c r="B90" t="n">
+        <v>101619</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>671820</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6648296</v>
+      </c>
+      <c r="S90" t="n">
+        <v>5</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074625</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>137074615</v>
+      </c>
+      <c r="B91" t="n">
+        <v>87569</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>671855</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6648175</v>
+      </c>
+      <c r="S91" t="n">
+        <v>5</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137074615</t>
         </is>
@@ -10904,6 +11163,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87545</v>
+        <v>87546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87470</v>
+        <v>87471</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87635</v>
+        <v>87636</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87635</v>
+        <v>87636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87369</v>
+        <v>87370</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91639</v>
+        <v>91640</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91665</v>
+        <v>91666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137249193</v>
       </c>
       <c r="B62" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>137249194</v>
       </c>
       <c r="B63" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>137249195</v>
       </c>
       <c r="B64" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>137249196</v>
       </c>
       <c r="B65" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>137249197</v>
       </c>
       <c r="B66" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137249198</v>
       </c>
       <c r="B67" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>137249199</v>
       </c>
       <c r="B68" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>137249200</v>
       </c>
       <c r="B69" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137249201</v>
       </c>
       <c r="B70" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137249203</v>
       </c>
       <c r="B71" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>137249205</v>
       </c>
       <c r="B72" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>137249206</v>
       </c>
       <c r="B73" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>137064515</v>
       </c>
       <c r="B76" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>136844366</v>
       </c>
       <c r="B77" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>136844369</v>
       </c>
       <c r="B78" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>136844370</v>
       </c>
       <c r="B79" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>136844371</v>
       </c>
       <c r="B80" t="n">
-        <v>107126</v>
+        <v>107127</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136844368</v>
       </c>
       <c r="B81" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>136844348</v>
       </c>
       <c r="B85" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>136844359</v>
       </c>
       <c r="B86" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>136844365</v>
       </c>
       <c r="B87" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>137074572</v>
       </c>
       <c r="B88" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>137074620</v>
       </c>
       <c r="B89" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>137074625</v>
       </c>
       <c r="B90" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>137074615</v>
       </c>
       <c r="B91" t="n">
-        <v>87569</v>
+        <v>87570</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87546</v>
+        <v>87549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87471</v>
+        <v>87474</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87636</v>
+        <v>87639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87636</v>
+        <v>87639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87370</v>
+        <v>87373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93452</v>
+        <v>93457</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93452</v>
+        <v>93457</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91640</v>
+        <v>91643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91666</v>
+        <v>91669</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137249193</v>
       </c>
       <c r="B62" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>137249194</v>
       </c>
       <c r="B63" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>137249195</v>
       </c>
       <c r="B64" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>137249196</v>
       </c>
       <c r="B65" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>137249197</v>
       </c>
       <c r="B66" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137249198</v>
       </c>
       <c r="B67" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>137249199</v>
       </c>
       <c r="B68" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>137249200</v>
       </c>
       <c r="B69" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137249201</v>
       </c>
       <c r="B70" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137249203</v>
       </c>
       <c r="B71" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>137249205</v>
       </c>
       <c r="B72" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>137249206</v>
       </c>
       <c r="B73" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>137064515</v>
       </c>
       <c r="B76" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>136844366</v>
       </c>
       <c r="B77" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>136844369</v>
       </c>
       <c r="B78" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>136844370</v>
       </c>
       <c r="B79" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>136844371</v>
       </c>
       <c r="B80" t="n">
-        <v>107127</v>
+        <v>107132</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136844368</v>
       </c>
       <c r="B81" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>136844348</v>
       </c>
       <c r="B85" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>136844359</v>
       </c>
       <c r="B86" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>136844365</v>
       </c>
       <c r="B87" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>137074572</v>
       </c>
       <c r="B88" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>137074620</v>
       </c>
       <c r="B89" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>137074625</v>
       </c>
       <c r="B90" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>137074615</v>
       </c>
       <c r="B91" t="n">
-        <v>87570</v>
+        <v>87573</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91669</v>
+        <v>91671</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137249193</v>
       </c>
       <c r="B62" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>137249194</v>
       </c>
       <c r="B63" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>137249195</v>
       </c>
       <c r="B64" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>137249196</v>
       </c>
       <c r="B65" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>137249197</v>
       </c>
       <c r="B66" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137249198</v>
       </c>
       <c r="B67" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>137249199</v>
       </c>
       <c r="B68" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>137249200</v>
       </c>
       <c r="B69" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137249201</v>
       </c>
       <c r="B70" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137249203</v>
       </c>
       <c r="B71" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>137249205</v>
       </c>
       <c r="B72" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>137249206</v>
       </c>
       <c r="B73" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>137064515</v>
       </c>
       <c r="B76" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>136844366</v>
       </c>
       <c r="B77" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>136844369</v>
       </c>
       <c r="B78" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>136844370</v>
       </c>
       <c r="B79" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>136844371</v>
       </c>
       <c r="B80" t="n">
-        <v>107132</v>
+        <v>107135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136844368</v>
       </c>
       <c r="B81" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>136844348</v>
       </c>
       <c r="B85" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>136844359</v>
       </c>
       <c r="B86" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>136844365</v>
       </c>
       <c r="B87" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>137074572</v>
       </c>
       <c r="B88" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>137074620</v>
       </c>
       <c r="B89" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>137074625</v>
       </c>
       <c r="B90" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87549</v>
+        <v>87554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87474</v>
+        <v>87479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87639</v>
+        <v>87644</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87639</v>
+        <v>87644</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87373</v>
+        <v>87378</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93459</v>
+        <v>93465</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93459</v>
+        <v>93465</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91645</v>
+        <v>91650</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91671</v>
+        <v>91676</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137249193</v>
       </c>
       <c r="B62" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>137249194</v>
       </c>
       <c r="B63" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>137249195</v>
       </c>
       <c r="B64" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>137249196</v>
       </c>
       <c r="B65" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>137249197</v>
       </c>
       <c r="B66" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137249198</v>
       </c>
       <c r="B67" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>137249199</v>
       </c>
       <c r="B68" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>137249200</v>
       </c>
       <c r="B69" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137249201</v>
       </c>
       <c r="B70" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137249203</v>
       </c>
       <c r="B71" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>137249205</v>
       </c>
       <c r="B72" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>137249206</v>
       </c>
       <c r="B73" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>137064515</v>
       </c>
       <c r="B76" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>136844366</v>
       </c>
       <c r="B77" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>136844369</v>
       </c>
       <c r="B78" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>136844370</v>
       </c>
       <c r="B79" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>136844371</v>
       </c>
       <c r="B80" t="n">
-        <v>107135</v>
+        <v>107141</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136844368</v>
       </c>
       <c r="B81" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>136844348</v>
       </c>
       <c r="B85" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>136844359</v>
       </c>
       <c r="B86" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>136844365</v>
       </c>
       <c r="B87" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>137074572</v>
       </c>
       <c r="B88" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>137074620</v>
       </c>
       <c r="B89" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>137074625</v>
       </c>
       <c r="B90" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>137074615</v>
       </c>
       <c r="B91" t="n">
-        <v>87573</v>
+        <v>87578</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -9355,7 +9355,7 @@
         <v>136844366</v>
       </c>
       <c r="B77" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>136844369</v>
       </c>
       <c r="B78" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>136844370</v>
       </c>
       <c r="B79" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>136844371</v>
       </c>
       <c r="B80" t="n">
-        <v>107141</v>
+        <v>107142</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136844368</v>
       </c>
       <c r="B81" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87554</v>
+        <v>87565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87479</v>
+        <v>87490</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87644</v>
+        <v>87655</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87644</v>
+        <v>87655</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87378</v>
+        <v>87389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93465</v>
+        <v>93477</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93465</v>
+        <v>93477</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93481</v>
+        <v>93493</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91650</v>
+        <v>91662</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91676</v>
+        <v>91688</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137249193</v>
       </c>
       <c r="B62" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>137249194</v>
       </c>
       <c r="B63" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>137249195</v>
       </c>
       <c r="B64" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>137249196</v>
       </c>
       <c r="B65" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>137249197</v>
       </c>
       <c r="B66" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137249198</v>
       </c>
       <c r="B67" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>137249199</v>
       </c>
       <c r="B68" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>137249200</v>
       </c>
       <c r="B69" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137249201</v>
       </c>
       <c r="B70" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137249203</v>
       </c>
       <c r="B71" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>137249205</v>
       </c>
       <c r="B72" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>137249206</v>
       </c>
       <c r="B73" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>137064515</v>
       </c>
       <c r="B76" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>136844366</v>
       </c>
       <c r="B77" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>136844369</v>
       </c>
       <c r="B78" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>136844370</v>
       </c>
       <c r="B79" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>136844371</v>
       </c>
       <c r="B80" t="n">
-        <v>107142</v>
+        <v>107154</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136844368</v>
       </c>
       <c r="B81" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>136844348</v>
       </c>
       <c r="B85" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>136844359</v>
       </c>
       <c r="B86" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>136844365</v>
       </c>
       <c r="B87" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>137074572</v>
       </c>
       <c r="B88" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>137074620</v>
       </c>
       <c r="B89" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>137074625</v>
       </c>
       <c r="B90" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>137074615</v>
       </c>
       <c r="B91" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87565</v>
+        <v>87566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136844352</v>
       </c>
       <c r="B3" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136844358</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136844364</v>
       </c>
       <c r="B5" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87655</v>
+        <v>87656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87655</v>
+        <v>87656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87389</v>
+        <v>87390</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91662</v>
+        <v>91663</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91688</v>
+        <v>91689</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         <v>136844361</v>
       </c>
       <c r="B40" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137249193</v>
       </c>
       <c r="B62" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>137249194</v>
       </c>
       <c r="B63" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>137249195</v>
       </c>
       <c r="B64" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>137249196</v>
       </c>
       <c r="B65" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>137249197</v>
       </c>
       <c r="B66" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137249198</v>
       </c>
       <c r="B67" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>137249199</v>
       </c>
       <c r="B68" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>137249200</v>
       </c>
       <c r="B69" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137249201</v>
       </c>
       <c r="B70" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137249203</v>
       </c>
       <c r="B71" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>137249205</v>
       </c>
       <c r="B72" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>137249206</v>
       </c>
       <c r="B73" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>137064515</v>
       </c>
       <c r="B76" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>136844366</v>
       </c>
       <c r="B77" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>136844369</v>
       </c>
       <c r="B78" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9602,7 +9602,7 @@
         <v>136844370</v>
       </c>
       <c r="B79" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>136844371</v>
       </c>
       <c r="B80" t="n">
-        <v>107154</v>
+        <v>107155</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         <v>136844368</v>
       </c>
       <c r="B81" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>104964</v>
+        <v>104965</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>136844348</v>
       </c>
       <c r="B85" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>136844359</v>
       </c>
       <c r="B86" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>136844365</v>
       </c>
       <c r="B87" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>137074572</v>
       </c>
       <c r="B88" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>137074620</v>
       </c>
       <c r="B89" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>137074625</v>
       </c>
       <c r="B90" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>137074615</v>
       </c>
       <c r="B91" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137074588</v>
       </c>
       <c r="B2" t="n">
-        <v>87566</v>
+        <v>87569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136975427</v>
       </c>
       <c r="B6" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975433</v>
       </c>
       <c r="B7" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975437</v>
       </c>
       <c r="B8" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975444</v>
       </c>
       <c r="B9" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975446</v>
       </c>
       <c r="B10" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137074577</v>
       </c>
       <c r="B11" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074598</v>
       </c>
       <c r="B12" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074599</v>
       </c>
       <c r="B13" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074600</v>
       </c>
       <c r="B14" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074609</v>
       </c>
       <c r="B15" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074611</v>
       </c>
       <c r="B16" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074573</v>
       </c>
       <c r="B17" t="n">
-        <v>87656</v>
+        <v>87659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>137074619</v>
       </c>
       <c r="B18" t="n">
-        <v>87656</v>
+        <v>87659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
         <v>137064512</v>
       </c>
       <c r="B19" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137074621</v>
       </c>
       <c r="B20" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>136975440</v>
       </c>
       <c r="B21" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975447</v>
       </c>
       <c r="B22" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137074601</v>
       </c>
       <c r="B23" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074617</v>
       </c>
       <c r="B24" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074618</v>
       </c>
       <c r="B25" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074622</v>
       </c>
       <c r="B26" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074628</v>
       </c>
       <c r="B27" t="n">
-        <v>87390</v>
+        <v>87393</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137064514</v>
       </c>
       <c r="B28" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3715,7 +3715,7 @@
         <v>137074612</v>
       </c>
       <c r="B29" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>136975443</v>
       </c>
       <c r="B30" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>137064508</v>
       </c>
       <c r="B33" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>137064519</v>
       </c>
       <c r="B34" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4383,7 +4383,7 @@
         <v>137074584</v>
       </c>
       <c r="B35" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4495,7 +4495,7 @@
         <v>137074604</v>
       </c>
       <c r="B36" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074592</v>
       </c>
       <c r="B37" t="n">
-        <v>91663</v>
+        <v>91666</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074636</v>
       </c>
       <c r="B38" t="n">
-        <v>91689</v>
+        <v>91692</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>136975430</v>
       </c>
       <c r="B41" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975432</v>
       </c>
       <c r="B42" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975436</v>
       </c>
       <c r="B43" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975439</v>
       </c>
       <c r="B44" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975452</v>
       </c>
       <c r="B45" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>137064507</v>
       </c>
       <c r="B46" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5734,7 +5734,7 @@
         <v>137064509</v>
       </c>
       <c r="B47" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>137064510</v>
       </c>
       <c r="B48" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>137064511</v>
       </c>
       <c r="B49" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>137064516</v>
       </c>
       <c r="B50" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         <v>137074569</v>
       </c>
       <c r="B51" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>137074576</v>
       </c>
       <c r="B52" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074581</v>
       </c>
       <c r="B53" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074582</v>
       </c>
       <c r="B54" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074586</v>
       </c>
       <c r="B55" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074594</v>
       </c>
       <c r="B56" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074596</v>
       </c>
       <c r="B57" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074602</v>
       </c>
       <c r="B58" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074605</v>
       </c>
       <c r="B59" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074608</v>
       </c>
       <c r="B60" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074630</v>
       </c>
       <c r="B61" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137249193</v>
       </c>
       <c r="B62" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         <v>137249194</v>
       </c>
       <c r="B63" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>137249195</v>
       </c>
       <c r="B64" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>137249196</v>
       </c>
       <c r="B65" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>137249197</v>
       </c>
       <c r="B66" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>137249198</v>
       </c>
       <c r="B67" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>137249199</v>
       </c>
       <c r="B68" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>137249200</v>
       </c>
       <c r="B69" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137249201</v>
       </c>
       <c r="B70" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>137249203</v>
       </c>
       <c r="B71" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>137249205</v>
       </c>
       <c r="B72" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>137249206</v>
       </c>
       <c r="B73" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9234,7 +9234,7 @@
         <v>137064515</v>
       </c>
       <c r="B76" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>136975429</v>
       </c>
       <c r="B82" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137064513</v>
       </c>
       <c r="B83" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10181,7 +10181,7 @@
         <v>137074607</v>
       </c>
       <c r="B84" t="n">
-        <v>104965</v>
+        <v>104968</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>137074572</v>
       </c>
       <c r="B88" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>137074620</v>
       </c>
       <c r="B89" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>137074625</v>
       </c>
       <c r="B90" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>137074615</v>
       </c>
       <c r="B91" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ91"/>
+  <dimension ref="A1:AZ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137074588</v>
+        <v>137498900</v>
       </c>
       <c r="B2" t="n">
-        <v>87569</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1988</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672005</v>
+        <v>671820</v>
       </c>
       <c r="R2" t="n">
-        <v>6648054</v>
+        <v>6648043</v>
       </c>
       <c r="S2" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,60 +780,60 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074588</t>
+          <t>https://artportalen.se/Sighting/137498900</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136844352</v>
+        <v>137074588</v>
       </c>
       <c r="B3" t="n">
-        <v>96643</v>
+        <v>87569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2812</v>
+        <v>1988</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672085</v>
+        <v>672005</v>
       </c>
       <c r="R3" t="n">
-        <v>6648168</v>
+        <v>6648054</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,24 +887,24 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844352</t>
+          <t>https://artportalen.se/Sighting/137074588</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136844358</v>
+        <v>136844352</v>
       </c>
       <c r="B4" t="n">
         <v>96643</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672071</v>
+        <v>672085</v>
       </c>
       <c r="R4" t="n">
-        <v>6648085</v>
+        <v>6648168</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,13 +1010,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844358</t>
+          <t>https://artportalen.se/Sighting/136844352</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136844364</v>
+        <v>136844358</v>
       </c>
       <c r="B5" t="n">
         <v>96643</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671939</v>
+        <v>672071</v>
       </c>
       <c r="R5" t="n">
-        <v>6648121</v>
+        <v>6648085</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,38 +1122,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844364</t>
+          <t>https://artportalen.se/Sighting/136844358</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136975427</v>
+        <v>136844364</v>
       </c>
       <c r="B6" t="n">
-        <v>87494</v>
+        <v>96643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3611</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsspindling</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cortinarius elegantior</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>671934</v>
+        <v>671939</v>
       </c>
       <c r="R6" t="n">
-        <v>6648022</v>
+        <v>6648121</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1193,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,24 +1223,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975427</t>
+          <t>https://artportalen.se/Sighting/136844364</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136975433</v>
+        <v>136975427</v>
       </c>
       <c r="B7" t="n">
         <v>87494</v>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672028</v>
+        <v>671934</v>
       </c>
       <c r="R7" t="n">
-        <v>6648071</v>
+        <v>6648022</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,13 +1346,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975433</t>
+          <t>https://artportalen.se/Sighting/136975427</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136975437</v>
+        <v>136975433</v>
       </c>
       <c r="B8" t="n">
         <v>87494</v>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672053</v>
+        <v>672028</v>
       </c>
       <c r="R8" t="n">
-        <v>6648081</v>
+        <v>6648071</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,13 +1458,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975437</t>
+          <t>https://artportalen.se/Sighting/136975433</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136975444</v>
+        <v>136975437</v>
       </c>
       <c r="B9" t="n">
         <v>87494</v>
@@ -1499,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672012</v>
+        <v>672053</v>
       </c>
       <c r="R9" t="n">
-        <v>6648146</v>
+        <v>6648081</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,13 +1570,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975444</t>
+          <t>https://artportalen.se/Sighting/136975437</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136975446</v>
+        <v>136975444</v>
       </c>
       <c r="B10" t="n">
         <v>87494</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>671945</v>
+        <v>672012</v>
       </c>
       <c r="R10" t="n">
-        <v>6648123</v>
+        <v>6648146</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,13 +1682,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975446</t>
+          <t>https://artportalen.se/Sighting/136975444</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137074577</v>
+        <v>136975446</v>
       </c>
       <c r="B11" t="n">
         <v>87494</v>
@@ -1719,17 +1719,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672048</v>
+        <v>671945</v>
       </c>
       <c r="R11" t="n">
-        <v>6648081</v>
+        <v>6648123</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,22 +1753,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,19 +1788,19 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074577</t>
+          <t>https://artportalen.se/Sighting/136975446</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137074598</v>
+        <v>137074577</v>
       </c>
       <c r="B12" t="n">
         <v>87494</v>
@@ -1835,13 +1835,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671941</v>
+        <v>672048</v>
       </c>
       <c r="R12" t="n">
-        <v>6648132</v>
+        <v>6648081</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1906,13 +1906,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074598</t>
+          <t>https://artportalen.se/Sighting/137074577</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137074599</v>
+        <v>137074598</v>
       </c>
       <c r="B13" t="n">
         <v>87494</v>
@@ -1950,10 +1950,10 @@
         <v>671941</v>
       </c>
       <c r="R13" t="n">
-        <v>6648015</v>
+        <v>6648132</v>
       </c>
       <c r="S13" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2018,13 +2018,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074599</t>
+          <t>https://artportalen.se/Sighting/137074598</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137074600</v>
+        <v>137074599</v>
       </c>
       <c r="B14" t="n">
         <v>87494</v>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>671934</v>
+        <v>671941</v>
       </c>
       <c r="R14" t="n">
-        <v>6648133</v>
+        <v>6648015</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2130,13 +2130,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074600</t>
+          <t>https://artportalen.se/Sighting/137074599</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137074609</v>
+        <v>137074600</v>
       </c>
       <c r="B15" t="n">
         <v>87494</v>
@@ -2171,10 +2171,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>671864</v>
+        <v>671934</v>
       </c>
       <c r="R15" t="n">
-        <v>6648176</v>
+        <v>6648133</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,13 +2242,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074609</t>
+          <t>https://artportalen.se/Sighting/137074600</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137074611</v>
+        <v>137074609</v>
       </c>
       <c r="B16" t="n">
         <v>87494</v>
@@ -2283,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>671857</v>
+        <v>671864</v>
       </c>
       <c r="R16" t="n">
-        <v>6648183</v>
+        <v>6648176</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,36 +2354,40 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074611</t>
+          <t>https://artportalen.se/Sighting/137074609</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137074573</v>
+        <v>137074611</v>
       </c>
       <c r="B17" t="n">
-        <v>87659</v>
+        <v>87494</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3624</v>
+        <v>3611</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Kungsspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Cortinarius elegantior</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2391,13 +2395,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672057</v>
+        <v>671857</v>
       </c>
       <c r="R17" t="n">
-        <v>6648177</v>
+        <v>6648183</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2426,7 +2430,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2436,7 +2440,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,13 +2466,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074573</t>
+          <t>https://artportalen.se/Sighting/137074611</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137074619</v>
+        <v>137074573</v>
       </c>
       <c r="B18" t="n">
         <v>87659</v>
@@ -2499,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>671847</v>
+        <v>672057</v>
       </c>
       <c r="R18" t="n">
-        <v>6648222</v>
+        <v>6648177</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2534,7 +2538,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2544,7 +2548,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2570,16 +2574,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074619</t>
+          <t>https://artportalen.se/Sighting/137074573</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137064512</v>
+        <v>137074619</v>
       </c>
       <c r="B19" t="n">
-        <v>87556</v>
+        <v>87659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2587,40 +2591,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3674</v>
+        <v>3624</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>671859</v>
+        <v>671847</v>
       </c>
       <c r="R19" t="n">
-        <v>6648162</v>
+        <v>6648222</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2649,7 +2646,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2659,7 +2656,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2668,35 +2665,30 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064512</t>
+          <t>https://artportalen.se/Sighting/137074619</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137074621</v>
+        <v>137064512</v>
       </c>
       <c r="B20" t="n">
         <v>87556</v>
@@ -2725,19 +2717,22 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>671821</v>
+        <v>671859</v>
       </c>
       <c r="R20" t="n">
-        <v>6648299</v>
+        <v>6648162</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2766,7 +2761,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2776,7 +2771,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2785,33 +2780,38 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074621</t>
+          <t>https://artportalen.se/Sighting/137064512</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136975440</v>
+        <v>137074621</v>
       </c>
       <c r="B21" t="n">
-        <v>87393</v>
+        <v>87556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2819,34 +2819,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3762</v>
+        <v>3674</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672040</v>
+        <v>671821</v>
       </c>
       <c r="R21" t="n">
-        <v>6648115</v>
+        <v>6648299</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2873,22 +2873,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2908,19 +2908,19 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975440</t>
+          <t>https://artportalen.se/Sighting/137074621</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136975447</v>
+        <v>136975440</v>
       </c>
       <c r="B22" t="n">
         <v>87393</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>671890</v>
+        <v>672040</v>
       </c>
       <c r="R22" t="n">
-        <v>6648080</v>
+        <v>6648115</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2990,7 +2990,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,13 +3026,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975447</t>
+          <t>https://artportalen.se/Sighting/136975440</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137074601</v>
+        <v>136975447</v>
       </c>
       <c r="B23" t="n">
         <v>87393</v>
@@ -3063,14 +3063,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>671933</v>
+        <v>671890</v>
       </c>
       <c r="R23" t="n">
-        <v>6648176</v>
+        <v>6648080</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3097,22 +3097,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,19 +3132,19 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074601</t>
+          <t>https://artportalen.se/Sighting/136975447</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137074617</v>
+        <v>137074601</v>
       </c>
       <c r="B24" t="n">
         <v>87393</v>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>671852</v>
+        <v>671933</v>
       </c>
       <c r="R24" t="n">
-        <v>6648189</v>
+        <v>6648176</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3214,7 +3214,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3250,13 +3250,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074617</t>
+          <t>https://artportalen.se/Sighting/137074601</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137074618</v>
+        <v>137074617</v>
       </c>
       <c r="B25" t="n">
         <v>87393</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>671851</v>
+        <v>671852</v>
       </c>
       <c r="R25" t="n">
-        <v>6648181</v>
+        <v>6648189</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3362,13 +3362,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074618</t>
+          <t>https://artportalen.se/Sighting/137074617</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137074622</v>
+        <v>137074618</v>
       </c>
       <c r="B26" t="n">
         <v>87393</v>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>671821</v>
+        <v>671851</v>
       </c>
       <c r="R26" t="n">
-        <v>6648299</v>
+        <v>6648181</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3438,7 +3438,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,13 +3474,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074622</t>
+          <t>https://artportalen.se/Sighting/137074618</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>137074628</v>
+        <v>137074622</v>
       </c>
       <c r="B27" t="n">
         <v>87393</v>
@@ -3515,10 +3515,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>671815</v>
+        <v>671821</v>
       </c>
       <c r="R27" t="n">
-        <v>6648070</v>
+        <v>6648299</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3550,7 +3550,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,16 +3586,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074628</t>
+          <t>https://artportalen.se/Sighting/137074622</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>137064514</v>
+        <v>137074628</v>
       </c>
       <c r="B28" t="n">
-        <v>93481</v>
+        <v>87393</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,40 +3603,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4363</v>
+        <v>3762</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>671858</v>
+        <v>671815</v>
       </c>
       <c r="R28" t="n">
-        <v>6648190</v>
+        <v>6648070</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3665,7 +3662,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3675,7 +3672,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,35 +3681,30 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064514</t>
+          <t>https://artportalen.se/Sighting/137074628</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137074612</v>
+        <v>137064514</v>
       </c>
       <c r="B29" t="n">
         <v>93481</v>
@@ -3741,19 +3733,22 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>671856</v>
+        <v>671858</v>
       </c>
       <c r="R29" t="n">
-        <v>6648181</v>
+        <v>6648190</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3782,7 +3777,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3792,7 +3787,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3801,71 +3796,76 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074612</t>
+          <t>https://artportalen.se/Sighting/137064514</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136975443</v>
+        <v>137074612</v>
       </c>
       <c r="B30" t="n">
-        <v>93497</v>
+        <v>93481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4366</v>
+        <v>4363</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672026</v>
+        <v>671856</v>
       </c>
       <c r="R30" t="n">
-        <v>6648149</v>
+        <v>6648181</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3889,22 +3889,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:16</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3924,44 +3924,44 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975443</t>
+          <t>https://artportalen.se/Sighting/137074612</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128261987</v>
+        <v>136975443</v>
       </c>
       <c r="B31" t="n">
-        <v>92869</v>
+        <v>93497</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3971,13 +3971,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>671861</v>
+        <v>672026</v>
       </c>
       <c r="R31" t="n">
-        <v>6648177</v>
+        <v>6648149</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4001,12 +4001,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4032,13 +4042,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261987</t>
+          <t>https://artportalen.se/Sighting/136975443</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128261988</v>
+        <v>128261987</v>
       </c>
       <c r="B32" t="n">
         <v>92869</v>
@@ -4073,10 +4083,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>671922</v>
+        <v>671861</v>
       </c>
       <c r="R32" t="n">
-        <v>6648158</v>
+        <v>6648177</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -4134,16 +4144,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128261988</t>
+          <t>https://artportalen.se/Sighting/128261987</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137064508</v>
+        <v>128261988</v>
       </c>
       <c r="B33" t="n">
-        <v>93156</v>
+        <v>92869</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4169,22 +4179,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672061</v>
+        <v>671922</v>
       </c>
       <c r="R33" t="n">
-        <v>6648256</v>
+        <v>6648158</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4208,22 +4215,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4232,35 +4229,30 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064508</t>
+          <t>https://artportalen.se/Sighting/128261988</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137064519</v>
+        <v>137064508</v>
       </c>
       <c r="B34" t="n">
         <v>93156</v>
@@ -4298,13 +4290,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>671801</v>
+        <v>672061</v>
       </c>
       <c r="R34" t="n">
-        <v>6648156</v>
+        <v>6648256</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4333,7 +4325,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4343,7 +4335,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4364,7 +4356,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4374,13 +4366,13 @@
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064519</t>
+          <t>https://artportalen.se/Sighting/137064508</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137074584</v>
+        <v>137064519</v>
       </c>
       <c r="B35" t="n">
         <v>93156</v>
@@ -4409,19 +4401,22 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672006</v>
+        <v>671801</v>
       </c>
       <c r="R35" t="n">
-        <v>6648070</v>
+        <v>6648156</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4450,7 +4445,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4460,7 +4455,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4469,30 +4464,35 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074584</t>
+          <t>https://artportalen.se/Sighting/137064519</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137074604</v>
+        <v>137074584</v>
       </c>
       <c r="B36" t="n">
         <v>93156</v>
@@ -4527,13 +4527,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>671908</v>
+        <v>672006</v>
       </c>
       <c r="R36" t="n">
-        <v>6647988</v>
+        <v>6648070</v>
       </c>
       <c r="S36" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4598,38 +4598,38 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074604</t>
+          <t>https://artportalen.se/Sighting/137074584</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137074592</v>
+        <v>137074604</v>
       </c>
       <c r="B37" t="n">
-        <v>91666</v>
+        <v>93156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5741</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4639,13 +4639,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>671999</v>
+        <v>671908</v>
       </c>
       <c r="R37" t="n">
-        <v>6648163</v>
+        <v>6647988</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4710,38 +4710,38 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074592</t>
+          <t>https://artportalen.se/Sighting/137074604</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137074636</v>
+        <v>137074592</v>
       </c>
       <c r="B38" t="n">
-        <v>91692</v>
+        <v>91666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>5741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4751,10 +4751,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>671767</v>
+        <v>671999</v>
       </c>
       <c r="R38" t="n">
-        <v>6648247</v>
+        <v>6648163</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4822,54 +4822,54 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074636</t>
+          <t>https://artportalen.se/Sighting/137074592</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128262008</v>
+        <v>137074636</v>
       </c>
       <c r="B39" t="n">
-        <v>91443</v>
+        <v>91692</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5754</v>
+        <v>5747</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>671851</v>
+        <v>671767</v>
       </c>
       <c r="R39" t="n">
-        <v>6648067</v>
+        <v>6648247</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4893,12 +4893,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4918,22 +4928,22 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128262008</t>
+          <t>https://artportalen.se/Sighting/137074636</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136844361</v>
+        <v>128262008</v>
       </c>
       <c r="B40" t="n">
-        <v>93518</v>
+        <v>91443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4941,46 +4951,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>671949</v>
+        <v>671851</v>
       </c>
       <c r="R40" t="n">
-        <v>6648020</v>
+        <v>6648067</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5004,22 +5005,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:52</t>
+          <t>2025-08-24</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5034,27 +5025,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844361</t>
+          <t>https://artportalen.se/Sighting/128262008</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136975430</v>
+        <v>136844361</v>
       </c>
       <c r="B41" t="n">
-        <v>93521</v>
+        <v>93518</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5079,17 +5070,26 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>671947</v>
+        <v>671949</v>
       </c>
       <c r="R41" t="n">
-        <v>6648018</v>
+        <v>6648020</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5116,22 +5116,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5146,24 +5146,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975430</t>
+          <t>https://artportalen.se/Sighting/136844361</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136975432</v>
+        <v>136975430</v>
       </c>
       <c r="B42" t="n">
         <v>93521</v>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672011</v>
+        <v>671947</v>
       </c>
       <c r="R42" t="n">
-        <v>6648066</v>
+        <v>6648018</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5269,13 +5269,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975432</t>
+          <t>https://artportalen.se/Sighting/136975430</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136975436</v>
+        <v>136975432</v>
       </c>
       <c r="B43" t="n">
         <v>93521</v>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672043</v>
+        <v>672011</v>
       </c>
       <c r="R43" t="n">
-        <v>6648077</v>
+        <v>6648066</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:58</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5381,13 +5381,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975436</t>
+          <t>https://artportalen.se/Sighting/136975432</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136975439</v>
+        <v>136975436</v>
       </c>
       <c r="B44" t="n">
         <v>93521</v>
@@ -5422,10 +5422,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672064</v>
+        <v>672043</v>
       </c>
       <c r="R44" t="n">
-        <v>6648093</v>
+        <v>6648077</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5493,13 +5493,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975439</t>
+          <t>https://artportalen.se/Sighting/136975436</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136975452</v>
+        <v>136975439</v>
       </c>
       <c r="B45" t="n">
         <v>93521</v>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>671811</v>
+        <v>672064</v>
       </c>
       <c r="R45" t="n">
-        <v>6648068</v>
+        <v>6648093</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5569,7 +5569,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5605,13 +5605,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975452</t>
+          <t>https://artportalen.se/Sighting/136975439</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>137064507</v>
+        <v>136975452</v>
       </c>
       <c r="B46" t="n">
         <v>93521</v>
@@ -5640,22 +5640,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>671946</v>
+        <v>671811</v>
       </c>
       <c r="R46" t="n">
-        <v>6648016</v>
+        <v>6648068</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5679,22 +5676,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5703,35 +5700,30 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064507</t>
+          <t>https://artportalen.se/Sighting/136975452</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>137064509</v>
+        <v>137064507</v>
       </c>
       <c r="B47" t="n">
         <v>93521</v>
@@ -5769,13 +5761,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>671985</v>
+        <v>671946</v>
       </c>
       <c r="R47" t="n">
-        <v>6648131</v>
+        <v>6648016</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5804,7 +5796,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5814,7 +5806,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5835,7 +5827,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5845,13 +5837,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064509</t>
+          <t>https://artportalen.se/Sighting/137064507</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>137064510</v>
+        <v>137064509</v>
       </c>
       <c r="B48" t="n">
         <v>93521</v>
@@ -5889,13 +5881,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672002</v>
+        <v>671985</v>
       </c>
       <c r="R48" t="n">
-        <v>6648119</v>
+        <v>6648131</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5924,7 +5916,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5934,7 +5926,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5955,7 +5947,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5965,13 +5957,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064510</t>
+          <t>https://artportalen.se/Sighting/137064509</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>137064511</v>
+        <v>137064510</v>
       </c>
       <c r="B49" t="n">
         <v>93521</v>
@@ -6009,13 +6001,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672003</v>
+        <v>672002</v>
       </c>
       <c r="R49" t="n">
-        <v>6648111</v>
+        <v>6648119</v>
       </c>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6044,7 +6036,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6054,7 +6046,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6075,7 +6067,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6085,13 +6077,13 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064511</t>
+          <t>https://artportalen.se/Sighting/137064510</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>137064516</v>
+        <v>137064511</v>
       </c>
       <c r="B50" t="n">
         <v>93521</v>
@@ -6129,13 +6121,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>671772</v>
+        <v>672003</v>
       </c>
       <c r="R50" t="n">
-        <v>6648263</v>
+        <v>6648111</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6164,7 +6156,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6174,7 +6166,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6195,7 +6187,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6205,13 +6197,13 @@
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064516</t>
+          <t>https://artportalen.se/Sighting/137064511</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>137074569</v>
+        <v>137064516</v>
       </c>
       <c r="B51" t="n">
         <v>93521</v>
@@ -6240,19 +6232,22 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672079</v>
+        <v>671772</v>
       </c>
       <c r="R51" t="n">
-        <v>6648133</v>
+        <v>6648263</v>
       </c>
       <c r="S51" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6281,7 +6276,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6291,7 +6286,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6300,30 +6295,35 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074569</t>
+          <t>https://artportalen.se/Sighting/137064516</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>137074576</v>
+        <v>137074569</v>
       </c>
       <c r="B52" t="n">
         <v>93521</v>
@@ -6358,13 +6358,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672052</v>
+        <v>672079</v>
       </c>
       <c r="R52" t="n">
-        <v>6648073</v>
+        <v>6648133</v>
       </c>
       <c r="S52" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6429,13 +6429,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074576</t>
+          <t>https://artportalen.se/Sighting/137074569</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>137074581</v>
+        <v>137074576</v>
       </c>
       <c r="B53" t="n">
         <v>93521</v>
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672029</v>
+        <v>672052</v>
       </c>
       <c r="R53" t="n">
-        <v>6648226</v>
+        <v>6648073</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6515,7 +6515,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6541,13 +6541,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074581</t>
+          <t>https://artportalen.se/Sighting/137074576</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>137074582</v>
+        <v>137074581</v>
       </c>
       <c r="B54" t="n">
         <v>93521</v>
@@ -6582,10 +6582,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672023</v>
+        <v>672029</v>
       </c>
       <c r="R54" t="n">
-        <v>6648149</v>
+        <v>6648226</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,13 +6653,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074582</t>
+          <t>https://artportalen.se/Sighting/137074581</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>137074586</v>
+        <v>137074582</v>
       </c>
       <c r="B55" t="n">
         <v>93521</v>
@@ -6694,10 +6694,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672005</v>
+        <v>672023</v>
       </c>
       <c r="R55" t="n">
-        <v>6648168</v>
+        <v>6648149</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6765,13 +6765,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074586</t>
+          <t>https://artportalen.se/Sighting/137074582</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>137074594</v>
+        <v>137074586</v>
       </c>
       <c r="B56" t="n">
         <v>93521</v>
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>671987</v>
+        <v>672005</v>
       </c>
       <c r="R56" t="n">
-        <v>6648165</v>
+        <v>6648168</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6877,13 +6877,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074594</t>
+          <t>https://artportalen.se/Sighting/137074586</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>137074596</v>
+        <v>137074594</v>
       </c>
       <c r="B57" t="n">
         <v>93521</v>
@@ -6918,13 +6918,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>671979</v>
+        <v>671987</v>
       </c>
       <c r="R57" t="n">
-        <v>6648089</v>
+        <v>6648165</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6989,13 +6989,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074596</t>
+          <t>https://artportalen.se/Sighting/137074594</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>137074602</v>
+        <v>137074596</v>
       </c>
       <c r="B58" t="n">
         <v>93521</v>
@@ -7030,10 +7030,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>671915</v>
+        <v>671979</v>
       </c>
       <c r="R58" t="n">
-        <v>6648009</v>
+        <v>6648089</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7075,7 +7075,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7101,13 +7101,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074602</t>
+          <t>https://artportalen.se/Sighting/137074596</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>137074605</v>
+        <v>137074602</v>
       </c>
       <c r="B59" t="n">
         <v>93521</v>
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>671905</v>
+        <v>671915</v>
       </c>
       <c r="R59" t="n">
-        <v>6647993</v>
+        <v>6648009</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7213,13 +7213,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074605</t>
+          <t>https://artportalen.se/Sighting/137074602</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>137074608</v>
+        <v>137074605</v>
       </c>
       <c r="B60" t="n">
         <v>93521</v>
@@ -7254,13 +7254,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>671871</v>
+        <v>671905</v>
       </c>
       <c r="R60" t="n">
-        <v>6648175</v>
+        <v>6647993</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7325,13 +7325,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074608</t>
+          <t>https://artportalen.se/Sighting/137074605</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>137074630</v>
+        <v>137074608</v>
       </c>
       <c r="B61" t="n">
         <v>93521</v>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>671814</v>
+        <v>671871</v>
       </c>
       <c r="R61" t="n">
-        <v>6648075</v>
+        <v>6648175</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7437,13 +7437,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074630</t>
+          <t>https://artportalen.se/Sighting/137074608</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>137249193</v>
+        <v>137074630</v>
       </c>
       <c r="B62" t="n">
         <v>93521</v>
@@ -7471,29 +7471,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>671957</v>
+        <v>671814</v>
       </c>
       <c r="R62" t="n">
-        <v>6648013</v>
+        <v>6648075</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7522,7 +7513,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7532,12 +7523,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:03</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Många i en ring</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7552,24 +7538,24 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249193</t>
+          <t>https://artportalen.se/Sighting/137074630</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>137249194</v>
+        <v>137249193</v>
       </c>
       <c r="B63" t="n">
         <v>93521</v>
@@ -7599,29 +7585,27 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672003</v>
+        <v>671957</v>
       </c>
       <c r="R63" t="n">
-        <v>6648067</v>
+        <v>6648013</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7650,7 +7634,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7660,7 +7644,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
@@ -7674,7 +7658,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7689,20 +7672,16 @@
           <t>Gustav Bringby</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+      <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249194</t>
+          <t>https://artportalen.se/Sighting/137249193</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>137249195</v>
+        <v>137249194</v>
       </c>
       <c r="B64" t="n">
         <v>93521</v>
@@ -7732,7 +7711,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>90</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -7748,13 +7727,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672048</v>
+        <v>672003</v>
       </c>
       <c r="R64" t="n">
-        <v>6648057</v>
+        <v>6648067</v>
       </c>
       <c r="S64" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7783,7 +7762,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7793,12 +7772,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ring</t>
+          <t>Många i en ring</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7829,13 +7808,13 @@
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249195</t>
+          <t>https://artportalen.se/Sighting/137249194</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>137249196</v>
+        <v>137249195</v>
       </c>
       <c r="B65" t="n">
         <v>93521</v>
@@ -7865,7 +7844,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -7881,13 +7860,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672056</v>
+        <v>672048</v>
       </c>
       <c r="R65" t="n">
-        <v>6648064</v>
+        <v>6648057</v>
       </c>
       <c r="S65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7916,7 +7895,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7926,12 +7905,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Stor ring</t>
+          <t>Ring</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7962,13 +7941,13 @@
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249196</t>
+          <t>https://artportalen.se/Sighting/137249195</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>137249197</v>
+        <v>137249196</v>
       </c>
       <c r="B66" t="n">
         <v>93521</v>
@@ -7998,7 +7977,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8014,13 +7993,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672057</v>
+        <v>672056</v>
       </c>
       <c r="R66" t="n">
-        <v>6648104</v>
+        <v>6648064</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8049,7 +8028,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8059,7 +8038,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Stor ring</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8090,13 +8074,13 @@
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249197</t>
+          <t>https://artportalen.se/Sighting/137249196</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>137249198</v>
+        <v>137249197</v>
       </c>
       <c r="B67" t="n">
         <v>93521</v>
@@ -8126,7 +8110,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8142,13 +8126,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672062</v>
+        <v>672057</v>
       </c>
       <c r="R67" t="n">
-        <v>6648106</v>
+        <v>6648104</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8177,7 +8161,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8187,12 +8171,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:45</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>På rad</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8223,13 +8202,13 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249198</t>
+          <t>https://artportalen.se/Sighting/137249197</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>137249199</v>
+        <v>137249198</v>
       </c>
       <c r="B68" t="n">
         <v>93521</v>
@@ -8259,7 +8238,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8275,13 +8254,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672047</v>
+        <v>672062</v>
       </c>
       <c r="R68" t="n">
-        <v>6648144</v>
+        <v>6648106</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8310,7 +8289,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8320,7 +8299,12 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På rad</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8351,13 +8335,13 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249199</t>
+          <t>https://artportalen.se/Sighting/137249198</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>137249200</v>
+        <v>137249199</v>
       </c>
       <c r="B69" t="n">
         <v>93521</v>
@@ -8387,7 +8371,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8403,13 +8387,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>671941</v>
+        <v>672047</v>
       </c>
       <c r="R69" t="n">
-        <v>6648170</v>
+        <v>6648144</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8438,7 +8422,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8448,7 +8432,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8479,13 +8463,13 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249200</t>
+          <t>https://artportalen.se/Sighting/137249199</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>137249201</v>
+        <v>137249200</v>
       </c>
       <c r="B70" t="n">
         <v>93521</v>
@@ -8515,7 +8499,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -8531,13 +8515,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>671896</v>
+        <v>671941</v>
       </c>
       <c r="R70" t="n">
-        <v>6648164</v>
+        <v>6648170</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8566,7 +8550,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8576,12 +8560,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ring</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8612,13 +8591,13 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249201</t>
+          <t>https://artportalen.se/Sighting/137249200</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>137249203</v>
+        <v>137249201</v>
       </c>
       <c r="B71" t="n">
         <v>93521</v>
@@ -8648,7 +8627,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8664,13 +8643,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>671819</v>
+        <v>671896</v>
       </c>
       <c r="R71" t="n">
-        <v>6648202</v>
+        <v>6648164</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8699,7 +8678,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8709,12 +8688,12 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Rad</t>
+          <t>Ring</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8745,13 +8724,13 @@
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249203</t>
+          <t>https://artportalen.se/Sighting/137249201</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>137249205</v>
+        <v>137249203</v>
       </c>
       <c r="B72" t="n">
         <v>93521</v>
@@ -8781,7 +8760,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8797,13 +8776,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>671781</v>
+        <v>671819</v>
       </c>
       <c r="R72" t="n">
-        <v>6648258</v>
+        <v>6648202</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8832,7 +8811,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8842,7 +8821,12 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Rad</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8873,13 +8857,13 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249205</t>
+          <t>https://artportalen.se/Sighting/137249203</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>137249206</v>
+        <v>137249205</v>
       </c>
       <c r="B73" t="n">
         <v>93521</v>
@@ -8909,7 +8893,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -8925,13 +8909,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>671771</v>
+        <v>671781</v>
       </c>
       <c r="R73" t="n">
-        <v>6648209</v>
+        <v>6648258</v>
       </c>
       <c r="S73" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8960,7 +8944,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8970,7 +8954,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9001,54 +8985,65 @@
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137249206</t>
+          <t>https://artportalen.se/Sighting/137249205</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>137074635</v>
+        <v>137249206</v>
       </c>
       <c r="B74" t="n">
-        <v>5188</v>
+        <v>93521</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>671776</v>
+        <v>671771</v>
       </c>
       <c r="R74" t="n">
-        <v>6648211</v>
+        <v>6648209</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9077,7 +9072,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9087,7 +9082,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9096,33 +9091,38 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074635</t>
+          <t>https://artportalen.se/Sighting/137249206</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>137074634</v>
+        <v>137074635</v>
       </c>
       <c r="B75" t="n">
-        <v>8459</v>
+        <v>5188</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9130,21 +9130,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>671787</v>
+        <v>671776</v>
       </c>
       <c r="R75" t="n">
-        <v>6648164</v>
+        <v>6648211</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9199,7 +9199,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9225,16 +9225,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074634</t>
+          <t>https://artportalen.se/Sighting/137074635</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>137064515</v>
+        <v>137074634</v>
       </c>
       <c r="B76" t="n">
-        <v>99457</v>
+        <v>8459</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9242,41 +9242,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219862</v>
+        <v>106554</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>671859</v>
+        <v>671787</v>
       </c>
       <c r="R76" t="n">
-        <v>6648188</v>
+        <v>6648164</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9305,7 +9301,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9315,7 +9311,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9324,85 +9320,75 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064515</t>
+          <t>https://artportalen.se/Sighting/137074634</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136844366</v>
+        <v>137064515</v>
       </c>
       <c r="B77" t="n">
-        <v>107155</v>
+        <v>99457</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220785</v>
+        <v>219862</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>671939</v>
+        <v>671859</v>
       </c>
       <c r="R77" t="n">
-        <v>6648124</v>
+        <v>6648188</v>
       </c>
       <c r="S77" t="n">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9426,22 +9412,22 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9450,30 +9436,35 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844366</t>
+          <t>https://artportalen.se/Sighting/137064515</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136844369</v>
+        <v>136844366</v>
       </c>
       <c r="B78" t="n">
         <v>107155</v>
@@ -9503,7 +9494,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -9517,13 +9508,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>671875</v>
+        <v>671939</v>
       </c>
       <c r="R78" t="n">
-        <v>6648159</v>
+        <v>6648124</v>
       </c>
       <c r="S78" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9552,7 +9543,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9562,12 +9553,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ej stora träd</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9593,13 +9579,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844369</t>
+          <t>https://artportalen.se/Sighting/136844366</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136844370</v>
+        <v>136844369</v>
       </c>
       <c r="B79" t="n">
         <v>107155</v>
@@ -9627,24 +9613,29 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>671879</v>
+        <v>671875</v>
       </c>
       <c r="R79" t="n">
-        <v>6648093</v>
+        <v>6648159</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9673,7 +9664,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9683,7 +9674,12 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ej stora träd</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9692,7 +9688,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9710,13 +9705,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844370</t>
+          <t>https://artportalen.se/Sighting/136844369</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136844371</v>
+        <v>136844370</v>
       </c>
       <c r="B80" t="n">
         <v>107155</v>
@@ -9745,16 +9740,20 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>671904</v>
+        <v>671879</v>
       </c>
       <c r="R80" t="n">
-        <v>6648132</v>
+        <v>6648093</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9786,7 +9785,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9796,12 +9795,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Litet träd</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9810,6 +9804,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -9827,33 +9822,33 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844371</t>
+          <t>https://artportalen.se/Sighting/136844370</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136844368</v>
+        <v>136844371</v>
       </c>
       <c r="B81" t="n">
-        <v>104965</v>
+        <v>107155</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9868,13 +9863,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>671875</v>
+        <v>671904</v>
       </c>
       <c r="R81" t="n">
-        <v>6648159</v>
+        <v>6648132</v>
       </c>
       <c r="S81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9903,7 +9898,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9913,7 +9908,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Litet träd</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9939,16 +9939,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844368</t>
+          <t>https://artportalen.se/Sighting/136844371</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136975429</v>
+        <v>136844368</v>
       </c>
       <c r="B82" t="n">
-        <v>104968</v>
+        <v>104965</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9980,13 +9980,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>671936</v>
+        <v>671875</v>
       </c>
       <c r="R82" t="n">
-        <v>6648021</v>
+        <v>6648159</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10010,22 +10010,22 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10040,24 +10040,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136975429</t>
+          <t>https://artportalen.se/Sighting/136844368</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>137064513</v>
+        <v>136975429</v>
       </c>
       <c r="B83" t="n">
         <v>104968</v>
@@ -10086,23 +10086,19 @@
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>671855</v>
+        <v>671936</v>
       </c>
       <c r="R83" t="n">
-        <v>6648166</v>
+        <v>6648021</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10126,22 +10122,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10150,35 +10146,30 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Nina Tadsen</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY83" t="inlineStr">
-        <is>
-          <t>Upplands kalkbarrskogar</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137064513</t>
+          <t>https://artportalen.se/Sighting/136975429</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>137074607</v>
+        <v>137064513</v>
       </c>
       <c r="B84" t="n">
         <v>104968</v>
@@ -10207,16 +10198,20 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>671884</v>
+        <v>671855</v>
       </c>
       <c r="R84" t="n">
-        <v>6647992</v>
+        <v>6648166</v>
       </c>
       <c r="S84" t="n">
         <v>6</v>
@@ -10248,7 +10243,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10258,7 +10253,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10267,33 +10262,38 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074607</t>
+          <t>https://artportalen.se/Sighting/137064513</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136844348</v>
+        <v>137074607</v>
       </c>
       <c r="B85" t="n">
-        <v>101647</v>
+        <v>104968</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10301,37 +10301,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Hammarbol, Upl</t>
+          <t>hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>671809</v>
+        <v>671884</v>
       </c>
       <c r="R85" t="n">
-        <v>6648285</v>
+        <v>6647992</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10355,22 +10355,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10385,24 +10385,24 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844348</t>
+          <t>https://artportalen.se/Sighting/137074607</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136844359</v>
+        <v>136844348</v>
       </c>
       <c r="B86" t="n">
         <v>101647</v>
@@ -10437,10 +10437,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672071</v>
+        <v>671809</v>
       </c>
       <c r="R86" t="n">
-        <v>6648085</v>
+        <v>6648285</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10472,7 +10472,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10508,13 +10508,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844359</t>
+          <t>https://artportalen.se/Sighting/136844348</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136844365</v>
+        <v>136844359</v>
       </c>
       <c r="B87" t="n">
         <v>101647</v>
@@ -10549,10 +10549,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>671944</v>
+        <v>672071</v>
       </c>
       <c r="R87" t="n">
-        <v>6648126</v>
+        <v>6648085</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10620,16 +10620,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136844365</t>
+          <t>https://artportalen.se/Sighting/136844359</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>137074572</v>
+        <v>136844365</v>
       </c>
       <c r="B88" t="n">
-        <v>101650</v>
+        <v>101647</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10657,14 +10657,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>hammarbol, Upl</t>
+          <t>Hammarbol, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672063</v>
+        <v>671944</v>
       </c>
       <c r="R88" t="n">
-        <v>6648246</v>
+        <v>6648126</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10691,22 +10691,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10721,24 +10721,24 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074572</t>
+          <t>https://artportalen.se/Sighting/136844365</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>137074620</v>
+        <v>137074572</v>
       </c>
       <c r="B89" t="n">
         <v>101650</v>
@@ -10773,10 +10773,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>671830</v>
+        <v>672063</v>
       </c>
       <c r="R89" t="n">
-        <v>6648024</v>
+        <v>6648246</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10844,13 +10844,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074620</t>
+          <t>https://artportalen.se/Sighting/137074572</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>137074625</v>
+        <v>137074620</v>
       </c>
       <c r="B90" t="n">
         <v>101650</v>
@@ -10885,10 +10885,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>671820</v>
+        <v>671830</v>
       </c>
       <c r="R90" t="n">
-        <v>6648296</v>
+        <v>6648024</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10920,7 +10920,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10956,38 +10956,38 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137074625</t>
+          <t>https://artportalen.se/Sighting/137074620</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>137074615</v>
+        <v>137074625</v>
       </c>
       <c r="B91" t="n">
-        <v>87593</v>
+        <v>101650</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6003295</v>
+        <v>222498</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10997,10 +10997,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>671855</v>
+        <v>671820</v>
       </c>
       <c r="R91" t="n">
-        <v>6648175</v>
+        <v>6648296</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11032,7 +11032,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11051,7 +11051,6 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -11068,6 +11067,119 @@
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137074625</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>137074615</v>
+      </c>
+      <c r="B92" t="n">
+        <v>87593</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>hammarbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>671855</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6648175</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Almunge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Tomas Falk, Nina Tadsen, Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137074615</t>
         </is>
@@ -11165,6 +11277,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -1243,7 +1243,7 @@
         <v>136975427</v>
       </c>
       <c r="B7" t="n">
-        <v>87494</v>
+        <v>87495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975433</v>
       </c>
       <c r="B8" t="n">
-        <v>87494</v>
+        <v>87495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975437</v>
       </c>
       <c r="B9" t="n">
-        <v>87494</v>
+        <v>87495</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975444</v>
       </c>
       <c r="B10" t="n">
-        <v>87494</v>
+        <v>87495</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136975446</v>
       </c>
       <c r="B11" t="n">
-        <v>87494</v>
+        <v>87495</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975440</v>
       </c>
       <c r="B22" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136975447</v>
       </c>
       <c r="B23" t="n">
-        <v>87393</v>
+        <v>87394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136975443</v>
       </c>
       <c r="B31" t="n">
-        <v>93497</v>
+        <v>93498</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975430</v>
       </c>
       <c r="B42" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975432</v>
       </c>
       <c r="B43" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975436</v>
       </c>
       <c r="B44" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975439</v>
       </c>
       <c r="B45" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>136975452</v>
       </c>
       <c r="B46" t="n">
-        <v>93521</v>
+        <v>93522</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>136975429</v>
       </c>
       <c r="B83" t="n">
-        <v>104968</v>
+        <v>104970</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/A 35260-2025 artfynd.xlsx
+++ b/artfynd/A 35260-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137498900</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137074588</v>
       </c>
       <c r="B3" t="n">
-        <v>87569</v>
+        <v>87573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136975427</v>
       </c>
       <c r="B7" t="n">
-        <v>87495</v>
+        <v>87498</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136975433</v>
       </c>
       <c r="B8" t="n">
-        <v>87495</v>
+        <v>87498</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136975437</v>
       </c>
       <c r="B9" t="n">
-        <v>87495</v>
+        <v>87498</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136975444</v>
       </c>
       <c r="B10" t="n">
-        <v>87495</v>
+        <v>87498</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136975446</v>
       </c>
       <c r="B11" t="n">
-        <v>87495</v>
+        <v>87498</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137074577</v>
       </c>
       <c r="B12" t="n">
-        <v>87494</v>
+        <v>87498</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137074598</v>
       </c>
       <c r="B13" t="n">
-        <v>87494</v>
+        <v>87498</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137074599</v>
       </c>
       <c r="B14" t="n">
-        <v>87494</v>
+        <v>87498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137074600</v>
       </c>
       <c r="B15" t="n">
-        <v>87494</v>
+        <v>87498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137074609</v>
       </c>
       <c r="B16" t="n">
-        <v>87494</v>
+        <v>87498</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137074611</v>
       </c>
       <c r="B17" t="n">
-        <v>87494</v>
+        <v>87498</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137074573</v>
       </c>
       <c r="B18" t="n">
-        <v>87659</v>
+        <v>87663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2583,7 +2583,7 @@
         <v>137074619</v>
       </c>
       <c r="B19" t="n">
-        <v>87659</v>
+        <v>87663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>137064512</v>
       </c>
       <c r="B20" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2811,7 +2811,7 @@
         <v>137074621</v>
       </c>
       <c r="B21" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>136975440</v>
       </c>
       <c r="B22" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>136975447</v>
       </c>
       <c r="B23" t="n">
-        <v>87394</v>
+        <v>87397</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137074601</v>
       </c>
       <c r="B24" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137074617</v>
       </c>
       <c r="B25" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>137074618</v>
       </c>
       <c r="B26" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3483,7 +3483,7 @@
         <v>137074622</v>
       </c>
       <c r="B27" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>137074628</v>
       </c>
       <c r="B28" t="n">
-        <v>87393</v>
+        <v>87397</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>137064514</v>
       </c>
       <c r="B29" t="n">
-        <v>93481</v>
+        <v>93485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -3827,7 +3827,7 @@
         <v>137074612</v>
       </c>
       <c r="B30" t="n">
-        <v>93481</v>
+        <v>93485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>136975443</v>
       </c>
       <c r="B31" t="n">
-        <v>93498</v>
+        <v>93501</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4255,7 +4255,7 @@
         <v>137064508</v>
       </c>
       <c r="B34" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
@@ -4375,7 +4375,7 @@
         <v>137064519</v>
       </c>
       <c r="B35" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4495,7 +4495,7 @@
         <v>137074584</v>
       </c>
       <c r="B36" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>137074604</v>
       </c>
       <c r="B37" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>137074592</v>
       </c>
       <c r="B38" t="n">
-        <v>91666</v>
+        <v>91670</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>137074636</v>
       </c>
       <c r="B39" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         <v>136975430</v>
       </c>
       <c r="B42" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         <v>136975432</v>
       </c>
       <c r="B43" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         <v>136975436</v>
       </c>
       <c r="B44" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         <v>136975439</v>
       </c>
       <c r="B45" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>136975452</v>
       </c>
       <c r="B46" t="n">
-        <v>93522</v>
+        <v>93525</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>137064507</v>
       </c>
       <c r="B47" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5846,7 +5846,7 @@
         <v>137064509</v>
       </c>
       <c r="B48" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5966,7 +5966,7 @@
         <v>137064510</v>
       </c>
       <c r="B49" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -6086,7 +6086,7 @@
         <v>137064511</v>
       </c>
       <c r="B50" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
@@ -6206,7 +6206,7 @@
         <v>137064516</v>
       </c>
       <c r="B51" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
@@ -6326,7 +6326,7 @@
         <v>137074569</v>
       </c>
       <c r="B52" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6438,7 +6438,7 @@
         <v>137074576</v>
       </c>
       <c r="B53" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6550,7 +6550,7 @@
         <v>137074581</v>
       </c>
       <c r="B54" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6662,7 +6662,7 @@
         <v>137074582</v>
       </c>
       <c r="B55" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>137074586</v>
       </c>
       <c r="B56" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>137074594</v>
       </c>
       <c r="B57" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>137074596</v>
       </c>
       <c r="B58" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>137074602</v>
       </c>
       <c r="B59" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>137074605</v>
       </c>
       <c r="B60" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>137074608</v>
       </c>
       <c r="B61" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>137074630</v>
       </c>
       <c r="B62" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>137249193</v>
       </c>
       <c r="B63" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>137249194</v>
       </c>
       <c r="B64" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>137249195</v>
       </c>
       <c r="B65" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>137249196</v>
       </c>
       <c r="B66" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>137249197</v>
       </c>
       <c r="B67" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         <v>137249198</v>
       </c>
       <c r="B68" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         <v>137249199</v>
       </c>
       <c r="B69" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>137249200</v>
       </c>
       <c r="B70" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>137249201</v>
       </c>
       <c r="B71" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>137249203</v>
       </c>
       <c r="B72" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>137249205</v>
       </c>
       <c r="B73" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>137249206</v>
       </c>
       <c r="B74" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>137064515</v>
       </c>
       <c r="B77" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
+          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -10060,7 +10060,7 @@
         <v>136975429</v>
       </c>
       <c r="B83" t="n">
-        <v>104970</v>
+        <v>104974</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>137064513</v>
       </c>
       <c r="B84" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Nina Tadsen, Tomas Falk, Gustav Bringby</t>
+          <t>Nina Tadsen, Gustav Bringby, Tomas Falk</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -10293,7 +10293,7 @@
         <v>137074607</v>
       </c>
       <c r="B85" t="n">
-        <v>104968</v>
+        <v>104974</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>137074572</v>
       </c>
       <c r="B89" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>137074620</v>
       </c>
       <c r="B90" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>137074625</v>
       </c>
       <c r="B91" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>137074615</v>
       </c>
       <c r="B92" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
